--- a/siglip_out_male.xlsx
+++ b/siglip_out_male.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF44"/>
+  <dimension ref="A1:AK44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,152 +429,177 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Modified\man1\male1_frillyflowerydress.png</t>
+          <t>male1\male1_cropped.jpg</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Modified\man1\male1_jewelry.png</t>
+          <t>male1\male1_have_jewerly.png</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Modified\man1\male1_longhair.png</t>
+          <t>male1\male1_have_makeup.png</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Modified\man1\male1_makeup.png</t>
+          <t>male1\male1_long_hair.png</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Modified\man1\male1_slightbuild.png</t>
+          <t>male1\male1_no_jewerly.png</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Modified\man2\male2_frillyflowerydress.png</t>
+          <t>male1\male1_no_makeup.png</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Modified\man2\male2_jewelry.png</t>
+          <t>male1\male1_short_hair.png</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Modified\man2\male2_longhair.png</t>
+          <t>male2\male2_have_jewerly.jpeg</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Modified\man2\male2_makeup.png</t>
+          <t>male2\male2_have_makeup.jpeg</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Modified\man2\male2_slightbuild.png</t>
+          <t>male2\male2_long_hair.jpeg</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Modified\man3\male3_frillyflowerydress.png</t>
+          <t>male2\male2_no_jewerly.jpeg</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Modified\man3\male3_jewelry.png</t>
+          <t>male2\male2_no_makeup.jpeg</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Modified\man3\male3_longhair.png</t>
+          <t>male2\male2_short_hair.jpeg</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Modified\man3\male3_makeup.png</t>
+          <t>male2\man2_cropped.jpg</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Modified\man3\male3_slightbuild.png</t>
+          <t>male3\male3_have_jewerly.jpeg</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Modified\man4\male4_frillyflowerydress.png</t>
+          <t>male3\male3_have_makeup.jpeg</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Modified\man4\male4_jewelry.png</t>
+          <t>male3\male3_long_hair.jpeg</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Modified\man4\male4_longhair.png</t>
+          <t>male3\male3_no_jewerly.jpeg</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Modified\man4\male4_makeup.png</t>
+          <t>male3\male3_no_makeup.jpeg</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Modified\man4\male4_slightbuild.png</t>
+          <t>male3\male3_short_hair.jpeg</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Modified\man5\male5_frillyflowerydress.png</t>
+          <t>male3\man3_cropped.jpg</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Modified\man5\male5_jewelry.png</t>
+          <t>male4\male4_have_jewerly.jpeg</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Modified\man5\male5_longhair.png</t>
+          <t>male4\male4_have_makeup.jpeg</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Modified\man5\male5_makeup.png</t>
+          <t>male4\male4_long_hair.jpeg</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Modified\man5\male5_slightbuild.png</t>
+          <t>male4\male4_no_jewerly.jpeg</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>man1.jpg</t>
+          <t>male4\male4_no_makeup.jpeg</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>man2.jpg</t>
+          <t>male4\male4_short_hair.jpeg</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>man3.jpg</t>
+          <t>male4\man4_cropped.jpg</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>man4.jpg</t>
+          <t>male5\male5_have_jewerly.jpeg</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>man5.png</t>
+          <t>male5\male5_have_makeup.jpeg</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>male5\male5_long_hair.jpeg</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>male5\male5_no_jewerly.jpeg</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>male5\male5_no_makeup.jpeg</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>male5\male5_short_hair.jpeg</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>male5\man5_cropped.png</t>
         </is>
       </c>
     </row>
@@ -590,94 +615,109 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.050920620561</v>
+        <v>0.06598823517560959</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07078582048400001</v>
+        <v>0.075053870677948</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06341952085499999</v>
+        <v>0.06529956310987473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06568004190899999</v>
+        <v>0.06569169461727142</v>
       </c>
       <c r="G2" t="n">
-        <v>0.064213089645</v>
+        <v>0.06475643068552017</v>
       </c>
       <c r="H2" t="n">
-        <v>0.061518188566</v>
+        <v>0.06821382790803909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.053313862532</v>
+        <v>0.06854724884033203</v>
       </c>
       <c r="J2" t="n">
-        <v>0.042867090553</v>
+        <v>0.06605979055166245</v>
       </c>
       <c r="K2" t="n">
-        <v>0.043340642005</v>
+        <v>0.06446037441492081</v>
       </c>
       <c r="L2" t="n">
-        <v>0.038561243564</v>
+        <v>0.04581724852323532</v>
       </c>
       <c r="M2" t="n">
-        <v>0.06521783769099999</v>
+        <v>0.06987340748310089</v>
       </c>
       <c r="N2" t="n">
-        <v>0.071139805019</v>
+        <v>0.07156726717948914</v>
       </c>
       <c r="O2" t="n">
-        <v>0.070339411497</v>
+        <v>0.07613683491945267</v>
       </c>
       <c r="P2" t="n">
-        <v>0.086235746741</v>
+        <v>0.06822395324707031</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.071109421551</v>
+        <v>0.06822279095649719</v>
       </c>
       <c r="R2" t="n">
-        <v>0.058542270213</v>
+        <v>0.06762544810771942</v>
       </c>
       <c r="S2" t="n">
-        <v>0.081010811031</v>
+        <v>0.07224468141794205</v>
       </c>
       <c r="T2" t="n">
-        <v>0.067191317677</v>
+        <v>0.05354667827486992</v>
       </c>
       <c r="U2" t="n">
-        <v>0.079053200781</v>
+        <v>0.06663636863231659</v>
       </c>
       <c r="V2" t="n">
-        <v>0.08120028674599999</v>
+        <v>0.06335883587598801</v>
       </c>
       <c r="W2" t="n">
-        <v>0.015899453312</v>
+        <v>0.06961054354906082</v>
       </c>
       <c r="X2" t="n">
-        <v>0.048197045922</v>
+        <v>0.07006560266017914</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05189697817</v>
+        <v>0.06483769416809082</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.046076174825</v>
+        <v>0.06202663853764534</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.051528804004</v>
+        <v>0.06764479726552963</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.058566950262</v>
+        <v>0.07519058138132095</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.081262685359</v>
+        <v>0.06736563891172409</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.068935386837</v>
+        <v>0.07188668847084045</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.061309210956</v>
+        <v>0.06107128784060478</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.034375011921</v>
+        <v>0.05477631837129593</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.05526154860854149</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.05166453123092651</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.04885818436741829</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.05083277449011803</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.06545953452587128</v>
       </c>
     </row>
     <row r="3">
@@ -692,94 +732,109 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.019742403179</v>
+        <v>0.04298749938607216</v>
       </c>
       <c r="D3" t="n">
-        <v>0.040223687887</v>
+        <v>0.0514775775372982</v>
       </c>
       <c r="E3" t="n">
-        <v>0.036497127265</v>
+        <v>0.04208948463201523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.040269911289</v>
+        <v>0.0421505980193615</v>
       </c>
       <c r="G3" t="n">
-        <v>0.037439405918</v>
+        <v>0.0412970744073391</v>
       </c>
       <c r="H3" t="n">
-        <v>0.035352066159</v>
+        <v>0.04456777125597</v>
       </c>
       <c r="I3" t="n">
-        <v>0.025563746691</v>
+        <v>0.04484688863158226</v>
       </c>
       <c r="J3" t="n">
-        <v>0.017528960481</v>
+        <v>0.03377405926585197</v>
       </c>
       <c r="K3" t="n">
-        <v>0.018325559795</v>
+        <v>0.03635727614164352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.014088708907</v>
+        <v>0.0262292418628931</v>
       </c>
       <c r="M3" t="n">
-        <v>0.036223251373</v>
+        <v>0.03462238237261772</v>
       </c>
       <c r="N3" t="n">
-        <v>0.037431176752</v>
+        <v>0.03671383485198021</v>
       </c>
       <c r="O3" t="n">
-        <v>0.040899164975</v>
+        <v>0.03983786702156067</v>
       </c>
       <c r="P3" t="n">
-        <v>0.054005701095</v>
+        <v>0.03352164104580879</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.037417426705</v>
+        <v>0.03684007376432419</v>
       </c>
       <c r="R3" t="n">
-        <v>0.020169993863</v>
+        <v>0.04051025211811066</v>
       </c>
       <c r="S3" t="n">
-        <v>0.051849864423</v>
+        <v>0.04677201807498932</v>
       </c>
       <c r="T3" t="n">
-        <v>0.046130500734</v>
+        <v>0.02661639451980591</v>
       </c>
       <c r="U3" t="n">
-        <v>0.049457781017</v>
+        <v>0.03645149990916252</v>
       </c>
       <c r="V3" t="n">
-        <v>0.049651794136</v>
+        <v>0.03605343401432037</v>
       </c>
       <c r="W3" t="n">
-        <v>0.000640474143</v>
+        <v>0.03583763539791107</v>
       </c>
       <c r="X3" t="n">
-        <v>0.022899860516</v>
+        <v>0.04182997345924377</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.025634167716</v>
+        <v>0.03765925019979477</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.017735656351</v>
+        <v>0.03431329503655434</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.027365816757</v>
+        <v>0.03772773593664169</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02872553654</v>
+        <v>0.0470288060605526</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.049187559634</v>
+        <v>0.04138202965259552</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.035847119987</v>
+        <v>0.04274871572852135</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.03398494795</v>
+        <v>0.02623968198895454</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0052450113</v>
+        <v>0.02731503173708916</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.02654758654534817</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.01894507929682732</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.01805425062775612</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.01536107156425714</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.03153844177722931</v>
       </c>
     </row>
     <row r="4">
@@ -794,94 +849,109 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.052560918033</v>
+        <v>0.05883991718292236</v>
       </c>
       <c r="D4" t="n">
-        <v>0.077271185815</v>
+        <v>0.07303044199943542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06695517897599999</v>
+        <v>0.064564548432827</v>
       </c>
       <c r="F4" t="n">
-        <v>0.075083486736</v>
+        <v>0.06289082765579224</v>
       </c>
       <c r="G4" t="n">
-        <v>0.067663520575</v>
+        <v>0.06028842926025391</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06638914346700001</v>
+        <v>0.06302840262651443</v>
       </c>
       <c r="I4" t="n">
-        <v>0.062313448638</v>
+        <v>0.06177841871976852</v>
       </c>
       <c r="J4" t="n">
-        <v>0.050873436034</v>
+        <v>0.06652406603097916</v>
       </c>
       <c r="K4" t="n">
-        <v>0.050685089082</v>
+        <v>0.06257812678813934</v>
       </c>
       <c r="L4" t="n">
-        <v>0.045142848045</v>
+        <v>0.04907852411270142</v>
       </c>
       <c r="M4" t="n">
-        <v>0.064127236605</v>
+        <v>0.06446687877178192</v>
       </c>
       <c r="N4" t="n">
-        <v>0.061468999833</v>
+        <v>0.0643359050154686</v>
       </c>
       <c r="O4" t="n">
-        <v>0.060450460762</v>
+        <v>0.06816683709621429</v>
       </c>
       <c r="P4" t="n">
-        <v>0.070103272796</v>
+        <v>0.06033453345298767</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.061425406486</v>
+        <v>0.06609491258859634</v>
       </c>
       <c r="R4" t="n">
-        <v>0.060816798359</v>
+        <v>0.06469473987817764</v>
       </c>
       <c r="S4" t="n">
-        <v>0.090258955956</v>
+        <v>0.07199316471815109</v>
       </c>
       <c r="T4" t="n">
-        <v>0.083040878177</v>
+        <v>0.05361736565828323</v>
       </c>
       <c r="U4" t="n">
-        <v>0.091424882412</v>
+        <v>0.06333208084106445</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08932030946</v>
+        <v>0.06039034202694893</v>
       </c>
       <c r="W4" t="n">
-        <v>0.022338621318</v>
+        <v>0.06223702803254128</v>
       </c>
       <c r="X4" t="n">
-        <v>0.055395700037</v>
+        <v>0.073948934674263</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.057319790125</v>
+        <v>0.06399570405483246</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.046409379691</v>
+        <v>0.06107709184288979</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.054940197617</v>
+        <v>0.06748367846012115</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.065187603235</v>
+        <v>0.07351365685462952</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.090309664607</v>
+        <v>0.06560899317264557</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.05977140367</v>
+        <v>0.07109009474515915</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.06738524883999999</v>
+        <v>0.05482779815793037</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.041727490723</v>
+        <v>0.05322658270597458</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.04941164702177048</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.04670599102973938</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.044599499553442</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.04826822876930237</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.05513410270214081</v>
       </c>
     </row>
     <row r="5">
@@ -896,94 +966,109 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.058835446835</v>
+        <v>0.06500107795000076</v>
       </c>
       <c r="D5" t="n">
-        <v>0.083117365837</v>
+        <v>0.06585077196359634</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07604930549900001</v>
+        <v>0.081482894718647</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08553833514500001</v>
+        <v>0.06464859843254089</v>
       </c>
       <c r="G5" t="n">
-        <v>0.072358928621</v>
+        <v>0.06282896548509598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.065870180726</v>
+        <v>0.06714846193790436</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06526426971</v>
+        <v>0.06913965940475464</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05363406986</v>
+        <v>0.07654749602079391</v>
       </c>
       <c r="K5" t="n">
-        <v>0.044789120555</v>
+        <v>0.07024341076612473</v>
       </c>
       <c r="L5" t="n">
-        <v>0.041883803904</v>
+        <v>0.05138618499040604</v>
       </c>
       <c r="M5" t="n">
-        <v>0.069125778973</v>
+        <v>0.07223188877105713</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06717326492099999</v>
+        <v>0.071917325258255</v>
       </c>
       <c r="O5" t="n">
-        <v>0.074873633683</v>
+        <v>0.07579154521226883</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08273822814200001</v>
+        <v>0.06683644652366638</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.07243702560699999</v>
+        <v>0.06943289190530777</v>
       </c>
       <c r="R5" t="n">
-        <v>0.071416586637</v>
+        <v>0.08536030352115631</v>
       </c>
       <c r="S5" t="n">
-        <v>0.110686592758</v>
+        <v>0.0836297795176506</v>
       </c>
       <c r="T5" t="n">
-        <v>0.101438820362</v>
+        <v>0.0621781162917614</v>
       </c>
       <c r="U5" t="n">
-        <v>0.111986644566</v>
+        <v>0.07149051874876022</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11039852351</v>
+        <v>0.0749540776014328</v>
       </c>
       <c r="W5" t="n">
-        <v>0.042994633317</v>
+        <v>0.07226154953241348</v>
       </c>
       <c r="X5" t="n">
-        <v>0.061232049018</v>
+        <v>0.0825570747256279</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.080693803728</v>
+        <v>0.08510830253362656</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.06586603820299999</v>
+        <v>0.07535281777381897</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.06717169284799999</v>
+        <v>0.07910217344760895</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.07580794394</v>
+        <v>0.08745016157627106</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.108612522483</v>
+        <v>0.08022090792655945</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.070674650371</v>
+        <v>0.08188501000404358</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.07060390710800001</v>
+        <v>0.05303394794464111</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.038144286722</v>
+        <v>0.05453839153051376</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.04808869212865829</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0439491793513298</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.0387587808072567</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.03967200219631195</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.06103470176458359</v>
       </c>
     </row>
     <row r="6">
@@ -998,94 +1083,109 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.017826231197</v>
+        <v>0.03347495198249817</v>
       </c>
       <c r="D6" t="n">
-        <v>0.03450710699</v>
+        <v>0.05038627237081528</v>
       </c>
       <c r="E6" t="n">
-        <v>0.026893589646</v>
+        <v>0.04443860426545143</v>
       </c>
       <c r="F6" t="n">
-        <v>0.034850567579</v>
+        <v>0.03643948212265968</v>
       </c>
       <c r="G6" t="n">
-        <v>0.024677107111</v>
+        <v>0.03215229883790016</v>
       </c>
       <c r="H6" t="n">
-        <v>0.024436820298</v>
+        <v>0.03622712194919586</v>
       </c>
       <c r="I6" t="n">
-        <v>0.007273294032</v>
+        <v>0.03293902054429054</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0011032084</v>
+        <v>0.03116621822118759</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002229720354</v>
+        <v>0.04600328952074051</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.007235246245</v>
+        <v>0.01485408935695887</v>
       </c>
       <c r="M6" t="n">
-        <v>0.029617415741</v>
+        <v>0.02608398720622063</v>
       </c>
       <c r="N6" t="n">
-        <v>0.022989824414</v>
+        <v>0.02880392037332058</v>
       </c>
       <c r="O6" t="n">
-        <v>0.032829545438</v>
+        <v>0.03090017847716808</v>
       </c>
       <c r="P6" t="n">
-        <v>0.038527406752</v>
+        <v>0.0248500369489193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02167622</v>
+        <v>0.03752203285694122</v>
       </c>
       <c r="R6" t="n">
-        <v>0.007213412318</v>
+        <v>0.05034133419394493</v>
       </c>
       <c r="S6" t="n">
-        <v>0.033051200211</v>
+        <v>0.04842440411448479</v>
       </c>
       <c r="T6" t="n">
-        <v>0.025150913745</v>
+        <v>0.02015412971377373</v>
       </c>
       <c r="U6" t="n">
-        <v>0.032315894961</v>
+        <v>0.03102770633995533</v>
       </c>
       <c r="V6" t="n">
-        <v>0.033802837133</v>
+        <v>0.02838114090263844</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.002316237893</v>
+        <v>0.03164156153798103</v>
       </c>
       <c r="X6" t="n">
-        <v>0.017716569826</v>
+        <v>0.04976007714867592</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.020493514836</v>
+        <v>0.06209380924701691</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.012914868072</v>
+        <v>0.04262927547097206</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.017654296011</v>
+        <v>0.04008328169584274</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.013624861836</v>
+        <v>0.04758744686841965</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.033599320799</v>
+        <v>0.03851284831762314</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.019205246121</v>
+        <v>0.04494474083185196</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.018215149641</v>
+        <v>0.02031392231583595</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.016182184219</v>
+        <v>0.02410819754004478</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.02515707165002823</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.01302570011466742</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.00700685428455472</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.006701200269162655</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.0263547133654356</v>
       </c>
     </row>
     <row r="7">
@@ -1100,94 +1200,109 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.049515556544</v>
+        <v>0.0777105987071991</v>
       </c>
       <c r="D7" t="n">
-        <v>0.093792535365</v>
+        <v>0.08319327235221863</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0863096416</v>
+        <v>0.08786731958389282</v>
       </c>
       <c r="F7" t="n">
-        <v>0.095917068422</v>
+        <v>0.07427627593278885</v>
       </c>
       <c r="G7" t="n">
-        <v>0.085556730628</v>
+        <v>0.07965210825204849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.070044822991</v>
+        <v>0.08191704750061035</v>
       </c>
       <c r="I7" t="n">
-        <v>0.063983254135</v>
+        <v>0.08056372404098511</v>
       </c>
       <c r="J7" t="n">
-        <v>0.057724345475</v>
+        <v>0.08851102739572525</v>
       </c>
       <c r="K7" t="n">
-        <v>0.048516988754</v>
+        <v>0.06283286958932877</v>
       </c>
       <c r="L7" t="n">
-        <v>0.044154521078</v>
+        <v>0.06002428010106087</v>
       </c>
       <c r="M7" t="n">
-        <v>0.07769113034</v>
+        <v>0.07846324890851974</v>
       </c>
       <c r="N7" t="n">
-        <v>0.096482463181</v>
+        <v>0.08048880100250244</v>
       </c>
       <c r="O7" t="n">
-        <v>0.101521059871</v>
+        <v>0.07807572931051254</v>
       </c>
       <c r="P7" t="n">
-        <v>0.103522211313</v>
+        <v>0.07177736610174179</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.098690725863</v>
+        <v>0.09192614257335663</v>
       </c>
       <c r="R7" t="n">
-        <v>0.059152062982</v>
+        <v>0.09360998868942261</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09855934232499999</v>
+        <v>0.09248261153697968</v>
       </c>
       <c r="T7" t="n">
-        <v>0.096151471138</v>
+        <v>0.08135952800512314</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09896402806</v>
+        <v>0.08994608372449875</v>
       </c>
       <c r="V7" t="n">
-        <v>0.097363397479</v>
+        <v>0.08436575531959534</v>
       </c>
       <c r="W7" t="n">
-        <v>0.028943482786</v>
+        <v>0.09142962098121643</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07130946964</v>
+        <v>0.0925193578004837</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.076422870159</v>
+        <v>0.08726507425308228</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.06660990417</v>
+        <v>0.08514457195997238</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.074461050332</v>
+        <v>0.09204086661338806</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.07788555324099999</v>
+        <v>0.09497625380754471</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.098883919418</v>
+        <v>0.08062106370925903</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.09372162073900001</v>
+        <v>0.09549667686223984</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.084150850773</v>
+        <v>0.05561915040016174</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.044256083667</v>
+        <v>0.06349477916955948</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.0700395479798317</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.05451754480600357</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.05239932984113693</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.05191190540790558</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.05858692526817322</v>
       </c>
     </row>
     <row r="8">
@@ -1202,94 +1317,109 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.08589287847300001</v>
+        <v>0.08383086323738098</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07805666327499999</v>
+        <v>0.09244103729724884</v>
       </c>
       <c r="E8" t="n">
-        <v>0.077280342579</v>
+        <v>0.09186643362045288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.087100364268</v>
+        <v>0.08722846955060959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.078337527812</v>
+        <v>0.07988986372947693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.091693758965</v>
+        <v>0.08370494097471237</v>
       </c>
       <c r="I8" t="n">
-        <v>0.060051452368</v>
+        <v>0.08377157151699066</v>
       </c>
       <c r="J8" t="n">
-        <v>0.054606523365</v>
+        <v>0.08245157450437546</v>
       </c>
       <c r="K8" t="n">
-        <v>0.051991611719</v>
+        <v>0.09211400896310806</v>
       </c>
       <c r="L8" t="n">
-        <v>0.047038089484</v>
+        <v>0.05604319274425507</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09159429371400001</v>
+        <v>0.07699902355670929</v>
       </c>
       <c r="N8" t="n">
-        <v>0.06833332776999999</v>
+        <v>0.07721523195505142</v>
       </c>
       <c r="O8" t="n">
-        <v>0.078980900347</v>
+        <v>0.07897094637155533</v>
       </c>
       <c r="P8" t="n">
-        <v>0.090054526925</v>
+        <v>0.07577509433031082</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.073652006686</v>
+        <v>0.0739586353302002</v>
       </c>
       <c r="R8" t="n">
-        <v>0.066538132727</v>
+        <v>0.09698227792978287</v>
       </c>
       <c r="S8" t="n">
-        <v>0.095420576632</v>
+        <v>0.09246191382408142</v>
       </c>
       <c r="T8" t="n">
-        <v>0.086556829512</v>
+        <v>0.06567281484603882</v>
       </c>
       <c r="U8" t="n">
-        <v>0.096321322024</v>
+        <v>0.07533378154039383</v>
       </c>
       <c r="V8" t="n">
-        <v>0.09660910815</v>
+        <v>0.07833544164896011</v>
       </c>
       <c r="W8" t="n">
-        <v>0.059851616621</v>
+        <v>0.07673995196819305</v>
       </c>
       <c r="X8" t="n">
-        <v>0.057305689901</v>
+        <v>0.09768155217170715</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.06624361127599999</v>
+        <v>0.1078838706016541</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.061484962702</v>
+        <v>0.08324919641017914</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.06295422464600001</v>
+        <v>0.08448591828346252</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.070618763566</v>
+        <v>0.09329523146152496</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.096638299525</v>
+        <v>0.08430058509111404</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.070364482701</v>
+        <v>0.09155262261629105</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.075505740941</v>
+        <v>0.07680460810661316</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.040247559547</v>
+        <v>0.06754834204912186</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.06718204170465469</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.05945718288421631</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.05270732194185257</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.05245393887162209</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.07956254482269287</v>
       </c>
     </row>
     <row r="9">
@@ -1304,94 +1434,109 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.057602345943</v>
+        <v>0.05227700248360634</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07096016407</v>
+        <v>0.05908884480595589</v>
       </c>
       <c r="E9" t="n">
-        <v>0.069928199053</v>
+        <v>0.05655945837497711</v>
       </c>
       <c r="F9" t="n">
-        <v>0.071643620729</v>
+        <v>0.05197387188673019</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06656746566299999</v>
+        <v>0.05135722085833549</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06834495067599999</v>
+        <v>0.05493016541004181</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0426383093</v>
+        <v>0.05707862228155136</v>
       </c>
       <c r="J9" t="n">
-        <v>0.039298053831</v>
+        <v>0.06442715972661972</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03568674624</v>
+        <v>0.05416383966803551</v>
       </c>
       <c r="L9" t="n">
-        <v>0.030227079988</v>
+        <v>0.04174995794892311</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06982415914499999</v>
+        <v>0.06223977357149124</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06431338190999999</v>
+        <v>0.06553055346012115</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07280993461599999</v>
+        <v>0.06745231151580811</v>
       </c>
       <c r="P9" t="n">
-        <v>0.08119904249899999</v>
+        <v>0.06090879440307617</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.06474762409900001</v>
+        <v>0.05801338702440262</v>
       </c>
       <c r="R9" t="n">
-        <v>0.054076902568</v>
+        <v>0.05826933681964874</v>
       </c>
       <c r="S9" t="n">
-        <v>0.080244868994</v>
+        <v>0.06007801741361618</v>
       </c>
       <c r="T9" t="n">
-        <v>0.077370494604</v>
+        <v>0.04186335206031799</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08206284046200001</v>
+        <v>0.05525285750627518</v>
       </c>
       <c r="V9" t="n">
-        <v>0.084950521588</v>
+        <v>0.05515969544649124</v>
       </c>
       <c r="W9" t="n">
-        <v>0.02303060703</v>
+        <v>0.05552259832620621</v>
       </c>
       <c r="X9" t="n">
-        <v>0.041296605021</v>
+        <v>0.06517378985881805</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.050132658333</v>
+        <v>0.06180312857031822</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.041583582759</v>
+        <v>0.06178295612335205</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.049246482551</v>
+        <v>0.06324264407157898</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.053801223636</v>
+        <v>0.06858180463314056</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.085538938642</v>
+        <v>0.06447428464889526</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.061724595726</v>
+        <v>0.06728468835353851</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.063527151942</v>
+        <v>0.04198246449232101</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.024934893474</v>
+        <v>0.04338813200592995</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.04387269169092178</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.03781574219465256</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.03541715443134308</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.02638326212763786</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.05207347124814987</v>
       </c>
     </row>
     <row r="10">
@@ -1406,94 +1551,109 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.076616927981</v>
+        <v>0.07040440291166306</v>
       </c>
       <c r="D10" t="n">
-        <v>0.067385368049</v>
+        <v>0.07934302091598511</v>
       </c>
       <c r="E10" t="n">
-        <v>0.063903257251</v>
+        <v>0.06873522698879242</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06661426276</v>
+        <v>0.0659257099032402</v>
       </c>
       <c r="G10" t="n">
-        <v>0.058535281569</v>
+        <v>0.06866560131311417</v>
       </c>
       <c r="H10" t="n">
-        <v>0.072583816946</v>
+        <v>0.07127584517002106</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04154509306</v>
+        <v>0.0712406188249588</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04550414905</v>
+        <v>0.06274770200252533</v>
       </c>
       <c r="K10" t="n">
-        <v>0.030009463429</v>
+        <v>0.06917717307806015</v>
       </c>
       <c r="L10" t="n">
-        <v>0.027142528445</v>
+        <v>0.03835272416472435</v>
       </c>
       <c r="M10" t="n">
-        <v>0.072385504842</v>
+        <v>0.06257742643356323</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06426688283699999</v>
+        <v>0.0635753870010376</v>
       </c>
       <c r="O10" t="n">
-        <v>0.077758342028</v>
+        <v>0.06321781128644943</v>
       </c>
       <c r="P10" t="n">
-        <v>0.07280252873900001</v>
+        <v>0.05766387283802032</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.06364197284000001</v>
+        <v>0.06648387759923935</v>
       </c>
       <c r="R10" t="n">
-        <v>0.054796680808</v>
+        <v>0.06719104200601578</v>
       </c>
       <c r="S10" t="n">
-        <v>0.076468147337</v>
+        <v>0.075518898665905</v>
       </c>
       <c r="T10" t="n">
-        <v>0.069065593183</v>
+        <v>0.04869688302278519</v>
       </c>
       <c r="U10" t="n">
-        <v>0.075968675315</v>
+        <v>0.05869618058204651</v>
       </c>
       <c r="V10" t="n">
-        <v>0.07378940284299999</v>
+        <v>0.05833781510591507</v>
       </c>
       <c r="W10" t="n">
-        <v>0.060158163309</v>
+        <v>0.0610613189637661</v>
       </c>
       <c r="X10" t="n">
-        <v>0.07968447357400001</v>
+        <v>0.09025571495294571</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.083119094372</v>
+        <v>0.07971154898405075</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.077001191676</v>
+        <v>0.06634543091058731</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.076554246247</v>
+        <v>0.06792132556438446</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.07485780865</v>
+        <v>0.07668187469244003</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.075889319181</v>
+        <v>0.06752197444438934</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.059853881598</v>
+        <v>0.07041267305612564</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.055864613503</v>
+        <v>0.03038605861365795</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.020645692945</v>
+        <v>0.04592463001608849</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.05580449104309082</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.02960130386054516</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.02724563889205456</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.03322363644838333</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.03924678266048431</v>
       </c>
     </row>
     <row r="11">
@@ -1508,94 +1668,109 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.045193213969</v>
+        <v>0.05822956934571266</v>
       </c>
       <c r="D11" t="n">
-        <v>0.053184181452</v>
+        <v>0.06760937720537186</v>
       </c>
       <c r="E11" t="n">
-        <v>0.051655523479</v>
+        <v>0.05540278553962708</v>
       </c>
       <c r="F11" t="n">
-        <v>0.052009824663</v>
+        <v>0.05786922574043274</v>
       </c>
       <c r="G11" t="n">
-        <v>0.050334431231</v>
+        <v>0.05673706531524658</v>
       </c>
       <c r="H11" t="n">
-        <v>0.067078061402</v>
+        <v>0.05958442389965057</v>
       </c>
       <c r="I11" t="n">
-        <v>0.021270617843</v>
+        <v>0.05980323255062103</v>
       </c>
       <c r="J11" t="n">
-        <v>0.025105724111</v>
+        <v>0.05881709605455399</v>
       </c>
       <c r="K11" t="n">
-        <v>0.019524535164</v>
+        <v>0.04636948555707932</v>
       </c>
       <c r="L11" t="n">
-        <v>0.015993148088</v>
+        <v>0.02216104790568352</v>
       </c>
       <c r="M11" t="n">
-        <v>0.057396475226</v>
+        <v>0.05178403109312057</v>
       </c>
       <c r="N11" t="n">
-        <v>0.05644037202</v>
+        <v>0.05313220620155334</v>
       </c>
       <c r="O11" t="n">
-        <v>0.053736295551</v>
+        <v>0.05016066133975983</v>
       </c>
       <c r="P11" t="n">
-        <v>0.066710427403</v>
+        <v>0.04921665787696838</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.054693799466</v>
+        <v>0.04667773842811584</v>
       </c>
       <c r="R11" t="n">
-        <v>0.046058319509</v>
+        <v>0.03991769254207611</v>
       </c>
       <c r="S11" t="n">
-        <v>0.08298946172</v>
+        <v>0.05645087733864784</v>
       </c>
       <c r="T11" t="n">
-        <v>0.06602538377</v>
+        <v>0.02829566411674023</v>
       </c>
       <c r="U11" t="n">
-        <v>0.080629833043</v>
+        <v>0.04702004790306091</v>
       </c>
       <c r="V11" t="n">
-        <v>0.079960636795</v>
+        <v>0.04138956964015961</v>
       </c>
       <c r="W11" t="n">
-        <v>0.021358793601</v>
+        <v>0.05044807866215706</v>
       </c>
       <c r="X11" t="n">
-        <v>0.05138669908</v>
+        <v>0.07594284415245056</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.051402449608</v>
+        <v>0.0533544085919857</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.048836663365</v>
+        <v>0.0520680695772171</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.052058145404</v>
+        <v>0.05632609501481056</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.060714811087</v>
+        <v>0.06368348002433777</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.082665808499</v>
+        <v>0.05376296117901802</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.050822835416</v>
+        <v>0.05859002470970154</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.048798210919</v>
+        <v>0.02836572006344795</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.010942356661</v>
+        <v>0.0348268561065197</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.03704020008444786</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.02526252344250679</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.01981503330171108</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.03147370368242264</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.03409608453512192</v>
       </c>
     </row>
     <row r="12">
@@ -1610,94 +1785,109 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.040063895285</v>
+        <v>0.03624510020017624</v>
       </c>
       <c r="D12" t="n">
-        <v>0.049886532128</v>
+        <v>0.03847208246588707</v>
       </c>
       <c r="E12" t="n">
-        <v>0.047618500888</v>
+        <v>0.04663588851690292</v>
       </c>
       <c r="F12" t="n">
-        <v>0.054783158004</v>
+        <v>0.04112889245152473</v>
       </c>
       <c r="G12" t="n">
-        <v>0.050313435495</v>
+        <v>0.03377237170934677</v>
       </c>
       <c r="H12" t="n">
-        <v>0.050639431924</v>
+        <v>0.03690329194068909</v>
       </c>
       <c r="I12" t="n">
-        <v>0.046281121671</v>
+        <v>0.04540910571813583</v>
       </c>
       <c r="J12" t="n">
-        <v>0.039677001536</v>
+        <v>0.04929912462830544</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04071142152</v>
+        <v>0.06796552240848541</v>
       </c>
       <c r="L12" t="n">
-        <v>0.035559341311</v>
+        <v>0.03055688366293907</v>
       </c>
       <c r="M12" t="n">
-        <v>0.048248987645</v>
+        <v>0.04480019584298134</v>
       </c>
       <c r="N12" t="n">
-        <v>0.036831170321</v>
+        <v>0.04493052884936333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.044991768897</v>
+        <v>0.05188174173235893</v>
       </c>
       <c r="P12" t="n">
-        <v>0.053077027202</v>
+        <v>0.04163302108645439</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.036183413118</v>
+        <v>0.03969501703977585</v>
       </c>
       <c r="R12" t="n">
-        <v>0.022835556418</v>
+        <v>0.06679268181324005</v>
       </c>
       <c r="S12" t="n">
-        <v>0.057764835656</v>
+        <v>0.06233825907111168</v>
       </c>
       <c r="T12" t="n">
-        <v>0.056744970381</v>
+        <v>0.02471063286066055</v>
       </c>
       <c r="U12" t="n">
-        <v>0.060628652573</v>
+        <v>0.04132263734936714</v>
       </c>
       <c r="V12" t="n">
-        <v>0.059169612825</v>
+        <v>0.04012738913297653</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.006779496558</v>
+        <v>0.04317393898963928</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03435594961</v>
+        <v>0.06346961855888367</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03423505649</v>
+        <v>0.09027555584907532</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.030919127166</v>
+        <v>0.04719846323132515</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.018763883039</v>
+        <v>0.0432872548699379</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.027733590454</v>
+        <v>0.05344694852828979</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.05832272023</v>
+        <v>0.05296581611037254</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.033089183271</v>
+        <v>0.046834547072649</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.04525160417</v>
+        <v>0.04318462312221527</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.023855898529</v>
+        <v>0.05229762941598892</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0.05651402473449707</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.03669450059533119</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.03201195597648621</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.02796963043510914</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.0525003969669342</v>
       </c>
     </row>
     <row r="13">
@@ -1712,94 +1902,109 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.087036900222</v>
+        <v>0.06916649639606476</v>
       </c>
       <c r="D13" t="n">
-        <v>0.067630127072</v>
+        <v>0.08115553110837936</v>
       </c>
       <c r="E13" t="n">
-        <v>0.062476426363</v>
+        <v>0.07871361821889877</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06424222886600001</v>
+        <v>0.07117385417222977</v>
       </c>
       <c r="G13" t="n">
-        <v>0.057598855346</v>
+        <v>0.06356469541788101</v>
       </c>
       <c r="H13" t="n">
-        <v>0.118995435536</v>
+        <v>0.06863963603973389</v>
       </c>
       <c r="I13" t="n">
-        <v>0.050473861396</v>
+        <v>0.06789185851812363</v>
       </c>
       <c r="J13" t="n">
-        <v>0.05480901897</v>
+        <v>0.08004876226186752</v>
       </c>
       <c r="K13" t="n">
-        <v>0.046179287136</v>
+        <v>0.08005397021770477</v>
       </c>
       <c r="L13" t="n">
-        <v>0.041544958949</v>
+        <v>0.06056134402751923</v>
       </c>
       <c r="M13" t="n">
-        <v>0.09562191367099999</v>
+        <v>0.06994490325450897</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06934498995500001</v>
+        <v>0.07116176933050156</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08201020211</v>
+        <v>0.07501830160617828</v>
       </c>
       <c r="P13" t="n">
-        <v>0.08467502892000001</v>
+        <v>0.06956428289413452</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.066882461309</v>
+        <v>0.07292885333299637</v>
       </c>
       <c r="R13" t="n">
-        <v>0.088558986783</v>
+        <v>0.09106719493865967</v>
       </c>
       <c r="S13" t="n">
-        <v>0.086232252419</v>
+        <v>0.08903779089450836</v>
       </c>
       <c r="T13" t="n">
-        <v>0.088348217309</v>
+        <v>0.05737941339612007</v>
       </c>
       <c r="U13" t="n">
-        <v>0.087242022157</v>
+        <v>0.07152203470468521</v>
       </c>
       <c r="V13" t="n">
-        <v>0.089153558016</v>
+        <v>0.07106343656778336</v>
       </c>
       <c r="W13" t="n">
-        <v>0.06341866403800001</v>
+        <v>0.07164186239242554</v>
       </c>
       <c r="X13" t="n">
-        <v>0.072457581758</v>
+        <v>0.09675344079732895</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.07589685916900001</v>
+        <v>0.08772079646587372</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.073145747185</v>
+        <v>0.07470958679914474</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.062284167856</v>
+        <v>0.07027886062860489</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.062184352428</v>
+        <v>0.07865971326828003</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.089615955949</v>
+        <v>0.07159669697284698</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.063546717167</v>
+        <v>0.07322733104228973</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.055688824505</v>
+        <v>0.05672319605946541</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.035781927407</v>
+        <v>0.06165327876806259</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.06788080930709839</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.04772435501217842</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.04071980714797974</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.04189121723175049</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.06268368661403656</v>
       </c>
     </row>
     <row r="14">
@@ -1814,94 +2019,109 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.061037432402</v>
+        <v>0.0548107773065567</v>
       </c>
       <c r="D14" t="n">
-        <v>0.061462327838</v>
+        <v>0.0579889677464962</v>
       </c>
       <c r="E14" t="n">
-        <v>0.058138664812</v>
+        <v>0.06312009692192078</v>
       </c>
       <c r="F14" t="n">
-        <v>0.065159022808</v>
+        <v>0.05119965970516205</v>
       </c>
       <c r="G14" t="n">
-        <v>0.062325134873</v>
+        <v>0.05338934808969498</v>
       </c>
       <c r="H14" t="n">
-        <v>0.068496823311</v>
+        <v>0.05693665519356728</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05865432322</v>
+        <v>0.05490083619952202</v>
       </c>
       <c r="J14" t="n">
-        <v>0.05588511005</v>
+        <v>0.05348197743296623</v>
       </c>
       <c r="K14" t="n">
-        <v>0.055273588747</v>
+        <v>0.06243718788027763</v>
       </c>
       <c r="L14" t="n">
-        <v>0.052364952862</v>
+        <v>0.03999406844377518</v>
       </c>
       <c r="M14" t="n">
-        <v>0.063402801752</v>
+        <v>0.0432414598762989</v>
       </c>
       <c r="N14" t="n">
-        <v>0.049787439406</v>
+        <v>0.04462041333317757</v>
       </c>
       <c r="O14" t="n">
-        <v>0.053434953094</v>
+        <v>0.04853605106472969</v>
       </c>
       <c r="P14" t="n">
-        <v>0.059995606542</v>
+        <v>0.03929918631911278</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.050564114004</v>
+        <v>0.05980642884969711</v>
       </c>
       <c r="R14" t="n">
-        <v>0.043687600642</v>
+        <v>0.06784599274396896</v>
       </c>
       <c r="S14" t="n">
-        <v>0.063346736133</v>
+        <v>0.06457474827766418</v>
       </c>
       <c r="T14" t="n">
-        <v>0.052153386176</v>
+        <v>0.04516446217894554</v>
       </c>
       <c r="U14" t="n">
-        <v>0.059458870441</v>
+        <v>0.05961192771792412</v>
       </c>
       <c r="V14" t="n">
-        <v>0.059489328414</v>
+        <v>0.05259199440479279</v>
       </c>
       <c r="W14" t="n">
-        <v>0.011505785398</v>
+        <v>0.06070885434746742</v>
       </c>
       <c r="X14" t="n">
-        <v>0.048137005419</v>
+        <v>0.06272868067026138</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.049976754934</v>
+        <v>0.07835491001605988</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.054415807128</v>
+        <v>0.05879880860447884</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.045364625752</v>
+        <v>0.0709063932299614</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.049728449434</v>
+        <v>0.07049071788787842</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.060078851879</v>
+        <v>0.05991025269031525</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.048621706665</v>
+        <v>0.06876253336668015</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.061238121241</v>
+        <v>0.04906231909990311</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.045181058347</v>
+        <v>0.05192001163959503</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.04860115796327591</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.04623578116297722</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.04427611082792282</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.04100725799798965</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.05652556195855141</v>
       </c>
     </row>
     <row r="15">
@@ -1916,94 +2136,109 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.007608460262</v>
+        <v>0.04388510063290596</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03977657482</v>
+        <v>0.05390872433781624</v>
       </c>
       <c r="E15" t="n">
-        <v>0.031533237547</v>
+        <v>0.03577163070440292</v>
       </c>
       <c r="F15" t="n">
-        <v>0.040323294699</v>
+        <v>0.03842587023973465</v>
       </c>
       <c r="G15" t="n">
-        <v>0.039107739925</v>
+        <v>0.03992933034896851</v>
       </c>
       <c r="H15" t="n">
-        <v>0.028327822685</v>
+        <v>0.04253391921520233</v>
       </c>
       <c r="I15" t="n">
-        <v>0.035367548466</v>
+        <v>0.0482766292989254</v>
       </c>
       <c r="J15" t="n">
-        <v>0.032467503101</v>
+        <v>0.03579510748386383</v>
       </c>
       <c r="K15" t="n">
-        <v>0.033533532172</v>
+        <v>0.01647084951400757</v>
       </c>
       <c r="L15" t="n">
-        <v>0.033086195588</v>
+        <v>0.02166839689016342</v>
       </c>
       <c r="M15" t="n">
-        <v>0.027111647651</v>
+        <v>0.02979649230837822</v>
       </c>
       <c r="N15" t="n">
-        <v>0.025491733104</v>
+        <v>0.03057011589407921</v>
       </c>
       <c r="O15" t="n">
-        <v>0.02360396646</v>
+        <v>0.04056710749864578</v>
       </c>
       <c r="P15" t="n">
-        <v>0.035947211087</v>
+        <v>0.02833547070622444</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.02287341468</v>
+        <v>0.03126440197229385</v>
       </c>
       <c r="R15" t="n">
-        <v>0.005591637455</v>
+        <v>0.02283038944005966</v>
       </c>
       <c r="S15" t="n">
-        <v>0.038047138602</v>
+        <v>0.03804779052734375</v>
       </c>
       <c r="T15" t="n">
-        <v>0.031033813953</v>
+        <v>0.0160421896725893</v>
       </c>
       <c r="U15" t="n">
-        <v>0.033806465566</v>
+        <v>0.02733779884874821</v>
       </c>
       <c r="V15" t="n">
-        <v>0.033291362226</v>
+        <v>0.03094755858182907</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.008773305453000001</v>
+        <v>0.0293857604265213</v>
       </c>
       <c r="X15" t="n">
-        <v>0.036474712193</v>
+        <v>0.05548175424337387</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.024468244985</v>
+        <v>0.03902783244848251</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.038663160056</v>
+        <v>0.03639198467135429</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.038096148521</v>
+        <v>0.04765749722719193</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.04246969521</v>
+        <v>0.0555841475725174</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.033569857478</v>
+        <v>0.05158305540680885</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02244322747</v>
+        <v>0.05061467736959457</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.037344712764</v>
+        <v>0.03492077067494392</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.029207784683</v>
+        <v>0.04174751415848732</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.0430087149143219</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0.03731953725218773</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.03593070060014725</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.04338191449642181</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.042958103120327</v>
       </c>
     </row>
     <row r="16">
@@ -2018,94 +2253,109 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.066246651113</v>
+        <v>0.04140685498714447</v>
       </c>
       <c r="D16" t="n">
-        <v>0.052070576698</v>
+        <v>0.05948178842663765</v>
       </c>
       <c r="E16" t="n">
-        <v>0.055061429739</v>
+        <v>0.06002334505319595</v>
       </c>
       <c r="F16" t="n">
-        <v>0.056134596467</v>
+        <v>0.05560624971985817</v>
       </c>
       <c r="G16" t="n">
-        <v>0.046985581517</v>
+        <v>0.04321346431970596</v>
       </c>
       <c r="H16" t="n">
-        <v>0.074841856956</v>
+        <v>0.04759251326322556</v>
       </c>
       <c r="I16" t="n">
-        <v>0.04018618539</v>
+        <v>0.04619547724723816</v>
       </c>
       <c r="J16" t="n">
-        <v>0.045814298093</v>
+        <v>0.04689549654722214</v>
       </c>
       <c r="K16" t="n">
-        <v>0.037499621511</v>
+        <v>0.08730965107679367</v>
       </c>
       <c r="L16" t="n">
-        <v>0.035556793213</v>
+        <v>0.04232535511255264</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06691975891599999</v>
+        <v>0.04357879608869553</v>
       </c>
       <c r="N16" t="n">
-        <v>0.054935961962</v>
+        <v>0.04640871286392212</v>
       </c>
       <c r="O16" t="n">
-        <v>0.061317548156</v>
+        <v>0.0382663868367672</v>
       </c>
       <c r="P16" t="n">
-        <v>0.077262446284</v>
+        <v>0.04018137976527214</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.053665719926</v>
+        <v>0.03513811156153679</v>
       </c>
       <c r="R16" t="n">
-        <v>0.061628252268</v>
+        <v>0.06263476610183716</v>
       </c>
       <c r="S16" t="n">
-        <v>0.06803023070100001</v>
+        <v>0.05967023968696594</v>
       </c>
       <c r="T16" t="n">
-        <v>0.065778493881</v>
+        <v>0.01659132726490498</v>
       </c>
       <c r="U16" t="n">
-        <v>0.066134743392</v>
+        <v>0.03066205978393555</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06411373615300001</v>
+        <v>0.02739114314317703</v>
       </c>
       <c r="W16" t="n">
-        <v>0.036942392588</v>
+        <v>0.03321439400315285</v>
       </c>
       <c r="X16" t="n">
-        <v>0.06573211401700001</v>
+        <v>0.05579885095357895</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.068402409554</v>
+        <v>0.08195696026086807</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.06717156618800001</v>
+        <v>0.0598573200404644</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.054577112198</v>
+        <v>0.05415092408657074</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.057875946164</v>
+        <v>0.05827848240733147</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.064337782562</v>
+        <v>0.05247116833925247</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.052469588816</v>
+        <v>0.05711972713470459</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.0463450104</v>
+        <v>0.03564811870455742</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.024239461869</v>
+        <v>0.04951523616909981</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0.04683021083474159</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.0312688946723938</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0.02867714315652847</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0.02244910411536694</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.03749815374612808</v>
       </c>
     </row>
     <row r="17">
@@ -2120,94 +2370,109 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.080755241215</v>
+        <v>0.08006350696086884</v>
       </c>
       <c r="D17" t="n">
-        <v>0.073295459151</v>
+        <v>0.08718793094158173</v>
       </c>
       <c r="E17" t="n">
-        <v>0.071627378464</v>
+        <v>0.08558015525341034</v>
       </c>
       <c r="F17" t="n">
-        <v>0.07843962311700001</v>
+        <v>0.08295763283967972</v>
       </c>
       <c r="G17" t="n">
-        <v>0.071944661438</v>
+        <v>0.07474155724048615</v>
       </c>
       <c r="H17" t="n">
-        <v>0.102193653584</v>
+        <v>0.07998766750097275</v>
       </c>
       <c r="I17" t="n">
-        <v>0.057396009564</v>
+        <v>0.07737968862056732</v>
       </c>
       <c r="J17" t="n">
-        <v>0.059142138809</v>
+        <v>0.05767654255032539</v>
       </c>
       <c r="K17" t="n">
-        <v>0.048933491111</v>
+        <v>0.0690227746963501</v>
       </c>
       <c r="L17" t="n">
-        <v>0.041144296527</v>
+        <v>0.04625909402966499</v>
       </c>
       <c r="M17" t="n">
-        <v>0.087073139846</v>
+        <v>0.05522467195987701</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06720960885299999</v>
+        <v>0.05690021812915802</v>
       </c>
       <c r="O17" t="n">
-        <v>0.079455301166</v>
+        <v>0.05830627679824829</v>
       </c>
       <c r="P17" t="n">
-        <v>0.088315501809</v>
+        <v>0.05286112800240517</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.070795156062</v>
+        <v>0.07015690952539444</v>
       </c>
       <c r="R17" t="n">
-        <v>0.070510476828</v>
+        <v>0.08460961282253265</v>
       </c>
       <c r="S17" t="n">
-        <v>0.077079623938</v>
+        <v>0.0947054848074913</v>
       </c>
       <c r="T17" t="n">
-        <v>0.074078731239</v>
+        <v>0.05774759873747826</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07660567015399999</v>
+        <v>0.073347307741642</v>
       </c>
       <c r="V17" t="n">
-        <v>0.075716458261</v>
+        <v>0.06924424320459366</v>
       </c>
       <c r="W17" t="n">
-        <v>0.066536918283</v>
+        <v>0.07211250066757202</v>
       </c>
       <c r="X17" t="n">
-        <v>0.06521808356</v>
+        <v>0.08580717444419861</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.07748424261799999</v>
+        <v>0.09239198267459869</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.07149577140799999</v>
+        <v>0.07140118628740311</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.070760123432</v>
+        <v>0.07194283604621887</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.070557072759</v>
+        <v>0.08372404426336288</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.076727814972</v>
+        <v>0.07148937880992889</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.066112212837</v>
+        <v>0.07737036794424057</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.07096303254399999</v>
+        <v>0.05818340927362442</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.037796135992</v>
+        <v>0.05322682857513428</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.0592518039047718</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.04819957539439201</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.04938783496618271</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.04383422061800957</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.06804907321929932</v>
       </c>
     </row>
     <row r="18">
@@ -2222,94 +2487,109 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.048699077219</v>
+        <v>0.05052675306797028</v>
       </c>
       <c r="D18" t="n">
-        <v>0.045104492456</v>
+        <v>0.04808174818754196</v>
       </c>
       <c r="E18" t="n">
-        <v>0.041228592396</v>
+        <v>0.06040547788143158</v>
       </c>
       <c r="F18" t="n">
-        <v>0.050383586437</v>
+        <v>0.04518769308924675</v>
       </c>
       <c r="G18" t="n">
-        <v>0.044014550745</v>
+        <v>0.04869483038783073</v>
       </c>
       <c r="H18" t="n">
-        <v>0.064552821219</v>
+        <v>0.05272533744573593</v>
       </c>
       <c r="I18" t="n">
-        <v>0.034556616098</v>
+        <v>0.05768518894910812</v>
       </c>
       <c r="J18" t="n">
-        <v>0.034413203597</v>
+        <v>0.05662041157484055</v>
       </c>
       <c r="K18" t="n">
-        <v>0.027981944382</v>
+        <v>0.04881396889686584</v>
       </c>
       <c r="L18" t="n">
-        <v>0.019724959508</v>
+        <v>0.02930538356304169</v>
       </c>
       <c r="M18" t="n">
-        <v>0.064887963235</v>
+        <v>0.05404083430767059</v>
       </c>
       <c r="N18" t="n">
-        <v>0.054264828563</v>
+        <v>0.05674934387207031</v>
       </c>
       <c r="O18" t="n">
-        <v>0.062032211572</v>
+        <v>0.05533816665410995</v>
       </c>
       <c r="P18" t="n">
-        <v>0.07476361841</v>
+        <v>0.04817882180213928</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.059807460755</v>
+        <v>0.06468003243207932</v>
       </c>
       <c r="R18" t="n">
-        <v>0.049484521151</v>
+        <v>0.06159502640366554</v>
       </c>
       <c r="S18" t="n">
-        <v>0.081670731306</v>
+        <v>0.06553426384925842</v>
       </c>
       <c r="T18" t="n">
-        <v>0.069155856967</v>
+        <v>0.05070041120052338</v>
       </c>
       <c r="U18" t="n">
-        <v>0.082085765898</v>
+        <v>0.0658458024263382</v>
       </c>
       <c r="V18" t="n">
-        <v>0.080977968872</v>
+        <v>0.06483415514230728</v>
       </c>
       <c r="W18" t="n">
-        <v>0.021204996854</v>
+        <v>0.0670938640832901</v>
       </c>
       <c r="X18" t="n">
-        <v>0.026865450665</v>
+        <v>0.07588923722505569</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.039655514061</v>
+        <v>0.06693597882986069</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.038526769727</v>
+        <v>0.0472506657242775</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.037470962852</v>
+        <v>0.06392648071050644</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.043083570898</v>
+        <v>0.07283786684274673</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.080711245537</v>
+        <v>0.06409303843975067</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.056724503636</v>
+        <v>0.06703336536884308</v>
       </c>
       <c r="AE18" t="n">
-        <v>0.040702581406</v>
+        <v>0.0460069514811039</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.014143362641</v>
+        <v>0.04654921218752861</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.04862650111317635</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.03879941627383232</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.03204461187124252</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.03615271300077438</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.05311517044901848</v>
       </c>
     </row>
     <row r="19">
@@ -2324,94 +2604,109 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.04486233741</v>
+        <v>0.06899137794971466</v>
       </c>
       <c r="D19" t="n">
-        <v>0.060738191009</v>
+        <v>0.08156665414571762</v>
       </c>
       <c r="E19" t="n">
-        <v>0.056590531021</v>
+        <v>0.07443422824144363</v>
       </c>
       <c r="F19" t="n">
-        <v>0.057962436229</v>
+        <v>0.07787097990512848</v>
       </c>
       <c r="G19" t="n">
-        <v>0.052478183061</v>
+        <v>0.06618835031986237</v>
       </c>
       <c r="H19" t="n">
-        <v>0.064714089036</v>
+        <v>0.07089484483003616</v>
       </c>
       <c r="I19" t="n">
-        <v>0.061343953013</v>
+        <v>0.07409434020519257</v>
       </c>
       <c r="J19" t="n">
-        <v>0.056876428425</v>
+        <v>0.06957826018333435</v>
       </c>
       <c r="K19" t="n">
-        <v>0.047553367913</v>
+        <v>0.0735643059015274</v>
       </c>
       <c r="L19" t="n">
-        <v>0.043355822563</v>
+        <v>0.0509449876844883</v>
       </c>
       <c r="M19" t="n">
-        <v>0.071273073554</v>
+        <v>0.05861033499240875</v>
       </c>
       <c r="N19" t="n">
-        <v>0.061847142875</v>
+        <v>0.06135495007038116</v>
       </c>
       <c r="O19" t="n">
-        <v>0.06971035897699999</v>
+        <v>0.06359649449586868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.08046296984</v>
+        <v>0.05871329456567764</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.061959493905</v>
+        <v>0.06577931344509125</v>
       </c>
       <c r="R19" t="n">
-        <v>0.052912861109</v>
+        <v>0.07143007218837738</v>
       </c>
       <c r="S19" t="n">
-        <v>0.077057659626</v>
+        <v>0.08474185317754745</v>
       </c>
       <c r="T19" t="n">
-        <v>0.06545242667200001</v>
+        <v>0.05061402171850204</v>
       </c>
       <c r="U19" t="n">
-        <v>0.074574775994</v>
+        <v>0.0646219477057457</v>
       </c>
       <c r="V19" t="n">
-        <v>0.073391437531</v>
+        <v>0.06649971008300781</v>
       </c>
       <c r="W19" t="n">
-        <v>0.033907599747</v>
+        <v>0.06572750955820084</v>
       </c>
       <c r="X19" t="n">
-        <v>0.059883572161</v>
+        <v>0.0719325989484787</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.06529160589000001</v>
+        <v>0.07298511266708374</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.058254390955</v>
+        <v>0.07069365680217743</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.059698559344</v>
+        <v>0.05984627082943916</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.055984906852</v>
+        <v>0.07123199105262756</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.072485454381</v>
+        <v>0.06816331297159195</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.060527514666</v>
+        <v>0.06611131876707077</v>
       </c>
       <c r="AE19" t="n">
-        <v>0.048305563629</v>
+        <v>0.06724650412797928</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.039322335273</v>
+        <v>0.05960320308804512</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.06199085712432861</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.05515261739492416</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.05314978584647179</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.0484185665845871</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.06722616404294968</v>
       </c>
     </row>
     <row r="20">
@@ -2426,94 +2721,109 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.031859502196</v>
+        <v>0.06910610944032669</v>
       </c>
       <c r="D20" t="n">
-        <v>0.08690187335000001</v>
+        <v>0.07641597837209702</v>
       </c>
       <c r="E20" t="n">
-        <v>0.079620271921</v>
+        <v>0.07328161597251892</v>
       </c>
       <c r="F20" t="n">
-        <v>0.086738705635</v>
+        <v>0.06523734331130981</v>
       </c>
       <c r="G20" t="n">
-        <v>0.081305712461</v>
+        <v>0.06614777445793152</v>
       </c>
       <c r="H20" t="n">
-        <v>0.057242810726</v>
+        <v>0.07064931094646454</v>
       </c>
       <c r="I20" t="n">
-        <v>0.055896986276</v>
+        <v>0.07118168473243713</v>
       </c>
       <c r="J20" t="n">
-        <v>0.053779739887</v>
+        <v>0.06099704280495644</v>
       </c>
       <c r="K20" t="n">
-        <v>0.049879767001</v>
+        <v>0.05403129756450653</v>
       </c>
       <c r="L20" t="n">
-        <v>0.047461289912</v>
+        <v>0.0464664027094841</v>
       </c>
       <c r="M20" t="n">
-        <v>0.060894276947</v>
+        <v>0.0569119043648243</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06222897768</v>
+        <v>0.05884338915348053</v>
       </c>
       <c r="O20" t="n">
-        <v>0.060857985169</v>
+        <v>0.06619082391262054</v>
       </c>
       <c r="P20" t="n">
-        <v>0.081802099943</v>
+        <v>0.05459965765476227</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.063832871616</v>
+        <v>0.06971598416566849</v>
       </c>
       <c r="R20" t="n">
-        <v>0.029378671199</v>
+        <v>0.07486758381128311</v>
       </c>
       <c r="S20" t="n">
-        <v>0.085191108286</v>
+        <v>0.07641309499740601</v>
       </c>
       <c r="T20" t="n">
-        <v>0.07577773183600001</v>
+        <v>0.05277363210916519</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08414322882899999</v>
+        <v>0.06707552075386047</v>
       </c>
       <c r="V20" t="n">
-        <v>0.085474073887</v>
+        <v>0.06812989711761475</v>
       </c>
       <c r="W20" t="n">
-        <v>0.018225923181</v>
+        <v>0.07187721133232117</v>
       </c>
       <c r="X20" t="n">
-        <v>0.07000912725900001</v>
+        <v>0.08513020724058151</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.066355369985</v>
+        <v>0.08288691937923431</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.071714669466</v>
+        <v>0.07597950845956802</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.068494573236</v>
+        <v>0.08420189470052719</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.06673556566199999</v>
+        <v>0.08900537341833115</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.085386872292</v>
+        <v>0.08191406726837158</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.060008179396</v>
+        <v>0.08475316315889359</v>
       </c>
       <c r="AE20" t="n">
-        <v>0.07828630507000001</v>
+        <v>0.05736839398741722</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.04109461233</v>
+        <v>0.06095557287335396</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.06545453518629074</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.05377638339996338</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.04583325982093811</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.04945463687181473</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.06521998345851898</v>
       </c>
     </row>
     <row r="21">
@@ -2528,94 +2838,109 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.037741065025</v>
+        <v>0.05540239810943604</v>
       </c>
       <c r="D21" t="n">
-        <v>0.061221491545</v>
+        <v>0.06554557383060455</v>
       </c>
       <c r="E21" t="n">
-        <v>0.057385794818</v>
+        <v>0.0582030862569809</v>
       </c>
       <c r="F21" t="n">
-        <v>0.061822682619</v>
+        <v>0.05742155760526657</v>
       </c>
       <c r="G21" t="n">
-        <v>0.056273397058</v>
+        <v>0.05867801234126091</v>
       </c>
       <c r="H21" t="n">
-        <v>0.047534950078</v>
+        <v>0.06308483332395554</v>
       </c>
       <c r="I21" t="n">
-        <v>0.050417385995</v>
+        <v>0.0617978647351265</v>
       </c>
       <c r="J21" t="n">
-        <v>0.045902449638</v>
+        <v>0.05917107313871384</v>
       </c>
       <c r="K21" t="n">
-        <v>0.042424738407</v>
+        <v>0.05336439609527588</v>
       </c>
       <c r="L21" t="n">
-        <v>0.036207042634</v>
+        <v>0.04373639449477196</v>
       </c>
       <c r="M21" t="n">
-        <v>0.054808355868</v>
+        <v>0.05340955033898354</v>
       </c>
       <c r="N21" t="n">
-        <v>0.064571306109</v>
+        <v>0.05562058463692665</v>
       </c>
       <c r="O21" t="n">
-        <v>0.06962573528300001</v>
+        <v>0.05253101885318756</v>
       </c>
       <c r="P21" t="n">
-        <v>0.072118155658</v>
+        <v>0.04683668166399002</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06600125879</v>
+        <v>0.06343954801559448</v>
       </c>
       <c r="R21" t="n">
-        <v>0.052020967007</v>
+        <v>0.04831397905945778</v>
       </c>
       <c r="S21" t="n">
-        <v>0.077638983727</v>
+        <v>0.05967264622449875</v>
       </c>
       <c r="T21" t="n">
-        <v>0.06905066222</v>
+        <v>0.04490084573626518</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07871247828</v>
+        <v>0.05975320935249329</v>
       </c>
       <c r="V21" t="n">
-        <v>0.075242377818</v>
+        <v>0.05084064602851868</v>
       </c>
       <c r="W21" t="n">
-        <v>0.019356399775</v>
+        <v>0.05929428339004517</v>
       </c>
       <c r="X21" t="n">
-        <v>0.053381055593</v>
+        <v>0.06520585715770721</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.060259625316</v>
+        <v>0.04608474299311638</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.065413787961</v>
+        <v>0.05379116907715797</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.06782066077</v>
+        <v>0.06606751680374146</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.06434842199099999</v>
+        <v>0.06596723198890686</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.07419159263400001</v>
+        <v>0.05545070022344589</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.063610300422</v>
+        <v>0.05971150100231171</v>
       </c>
       <c r="AE21" t="n">
-        <v>0.054725937545</v>
+        <v>0.03097694180905819</v>
       </c>
       <c r="AF21" t="n">
-        <v>0.033901162446</v>
+        <v>0.0399671345949173</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.04046930745244026</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.02898081764578819</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.02577982470393181</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.03782425448298454</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.03740465641021729</v>
       </c>
     </row>
     <row r="22">
@@ -2630,94 +2955,109 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.069478183985</v>
+        <v>0.07189667969942093</v>
       </c>
       <c r="D22" t="n">
-        <v>0.063441030681</v>
+        <v>0.08689247816801071</v>
       </c>
       <c r="E22" t="n">
-        <v>0.061092942953</v>
+        <v>0.07952158898115158</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06585721671600001</v>
+        <v>0.07295282185077667</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05744368583</v>
+        <v>0.0714491680264473</v>
       </c>
       <c r="H22" t="n">
-        <v>0.07676825672400001</v>
+        <v>0.07641148567199707</v>
       </c>
       <c r="I22" t="n">
-        <v>0.053834613413</v>
+        <v>0.0713794082403183</v>
       </c>
       <c r="J22" t="n">
-        <v>0.048763073981</v>
+        <v>0.06622501462697983</v>
       </c>
       <c r="K22" t="n">
-        <v>0.050108969212</v>
+        <v>0.06893510371446609</v>
       </c>
       <c r="L22" t="n">
-        <v>0.044404264539</v>
+        <v>0.04455231875181198</v>
       </c>
       <c r="M22" t="n">
-        <v>0.071810215712</v>
+        <v>0.06393362581729889</v>
       </c>
       <c r="N22" t="n">
-        <v>0.065204657614</v>
+        <v>0.06617122888565063</v>
       </c>
       <c r="O22" t="n">
-        <v>0.067572161555</v>
+        <v>0.06739968061447144</v>
       </c>
       <c r="P22" t="n">
-        <v>0.087881669402</v>
+        <v>0.06331843137741089</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.06588399410199999</v>
+        <v>0.06748566031455994</v>
       </c>
       <c r="R22" t="n">
-        <v>0.045338705182</v>
+        <v>0.0721886083483696</v>
       </c>
       <c r="S22" t="n">
-        <v>0.074049860239</v>
+        <v>0.07638582587242126</v>
       </c>
       <c r="T22" t="n">
-        <v>0.058391533792</v>
+        <v>0.05476800352334976</v>
       </c>
       <c r="U22" t="n">
-        <v>0.071156188846</v>
+        <v>0.06741563230752945</v>
       </c>
       <c r="V22" t="n">
-        <v>0.07154371589400001</v>
+        <v>0.06224262714385986</v>
       </c>
       <c r="W22" t="n">
-        <v>0.039684444666</v>
+        <v>0.06710676848888397</v>
       </c>
       <c r="X22" t="n">
-        <v>0.052731692791</v>
+        <v>0.07792361080646515</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.057742197067</v>
+        <v>0.07812625914812088</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.054734680802</v>
+        <v>0.06730552017688751</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.050869636238</v>
+        <v>0.07113039493560791</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.052663881332</v>
+        <v>0.07917312532663345</v>
       </c>
       <c r="AC22" t="n">
-        <v>0.071833193302</v>
+        <v>0.06502441316843033</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.063554391265</v>
+        <v>0.07410576194524765</v>
       </c>
       <c r="AE22" t="n">
-        <v>0.055107854307</v>
+        <v>0.05887467786669731</v>
       </c>
       <c r="AF22" t="n">
-        <v>0.037799350917</v>
+        <v>0.05975162982940674</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.05822262540459633</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.05156943202018738</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.04784377664327621</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.05085989832878113</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.06452792882919312</v>
       </c>
     </row>
     <row r="23">
@@ -2732,94 +3072,109 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.045809742063</v>
+        <v>0.06025499105453491</v>
       </c>
       <c r="D23" t="n">
-        <v>0.058659113944</v>
+        <v>0.07513697445392609</v>
       </c>
       <c r="E23" t="n">
-        <v>0.051310364157</v>
+        <v>0.06339486688375473</v>
       </c>
       <c r="F23" t="n">
-        <v>0.061676628888</v>
+        <v>0.06182412058115005</v>
       </c>
       <c r="G23" t="n">
-        <v>0.056718818843</v>
+        <v>0.05931206420063972</v>
       </c>
       <c r="H23" t="n">
-        <v>0.055312145501</v>
+        <v>0.06444128602743149</v>
       </c>
       <c r="I23" t="n">
-        <v>0.054053902626</v>
+        <v>0.06487336754798889</v>
       </c>
       <c r="J23" t="n">
-        <v>0.050246018916</v>
+        <v>0.06591906398534775</v>
       </c>
       <c r="K23" t="n">
-        <v>0.050416447222</v>
+        <v>0.0615973062813282</v>
       </c>
       <c r="L23" t="n">
-        <v>0.04423462227</v>
+        <v>0.0366838276386261</v>
       </c>
       <c r="M23" t="n">
-        <v>0.053725142032</v>
+        <v>0.05888840556144714</v>
       </c>
       <c r="N23" t="n">
-        <v>0.046828486025</v>
+        <v>0.06264741718769073</v>
       </c>
       <c r="O23" t="n">
-        <v>0.051079425961</v>
+        <v>0.06580058485269547</v>
       </c>
       <c r="P23" t="n">
-        <v>0.06576987355900001</v>
+        <v>0.05623926594853401</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.046804770827</v>
+        <v>0.05994965508580208</v>
       </c>
       <c r="R23" t="n">
-        <v>0.044067174196</v>
+        <v>0.06567635387182236</v>
       </c>
       <c r="S23" t="n">
-        <v>0.068051964045</v>
+        <v>0.06337921321392059</v>
       </c>
       <c r="T23" t="n">
-        <v>0.053709425032</v>
+        <v>0.04514608904719353</v>
       </c>
       <c r="U23" t="n">
-        <v>0.067939117551</v>
+        <v>0.05672907829284668</v>
       </c>
       <c r="V23" t="n">
-        <v>0.066682592034</v>
+        <v>0.06011561676859856</v>
       </c>
       <c r="W23" t="n">
-        <v>0.026643494144</v>
+        <v>0.05622490495443344</v>
       </c>
       <c r="X23" t="n">
-        <v>0.034101434052</v>
+        <v>0.07891813665628433</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.042646154761</v>
+        <v>0.07672456651926041</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.034901451319</v>
+        <v>0.05934609845280647</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.034114230424</v>
+        <v>0.06913124769926071</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.043253753334</v>
+        <v>0.07591430842876434</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.067745134234</v>
+        <v>0.0706375390291214</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.048158761114</v>
+        <v>0.07348648458719254</v>
       </c>
       <c r="AE23" t="n">
-        <v>0.056611929089</v>
+        <v>0.05344158038496971</v>
       </c>
       <c r="AF23" t="n">
-        <v>0.038930792361</v>
+        <v>0.05184656009078026</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.04922912269830704</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.04562868922948837</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0.04523670673370361</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0.04048363864421844</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0.05581298843026161</v>
       </c>
     </row>
     <row r="24">
@@ -2834,94 +3189,109 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.020514078438</v>
+        <v>0.03791452571749687</v>
       </c>
       <c r="D24" t="n">
-        <v>0.037170026451</v>
+        <v>0.05205359309911728</v>
       </c>
       <c r="E24" t="n">
-        <v>0.039621688426</v>
+        <v>0.04639409855008125</v>
       </c>
       <c r="F24" t="n">
-        <v>0.042120981961</v>
+        <v>0.03735606744885445</v>
       </c>
       <c r="G24" t="n">
-        <v>0.040298040956</v>
+        <v>0.04047610238194466</v>
       </c>
       <c r="H24" t="n">
-        <v>0.044846475124</v>
+        <v>0.04344505071640015</v>
       </c>
       <c r="I24" t="n">
-        <v>0.032407432795</v>
+        <v>0.04454084858298302</v>
       </c>
       <c r="J24" t="n">
-        <v>0.031209178269</v>
+        <v>0.048869539052248</v>
       </c>
       <c r="K24" t="n">
-        <v>0.030610091984</v>
+        <v>0.05561690405011177</v>
       </c>
       <c r="L24" t="n">
-        <v>0.027064949274</v>
+        <v>0.02985817193984985</v>
       </c>
       <c r="M24" t="n">
-        <v>0.034186698496</v>
+        <v>0.04447866976261139</v>
       </c>
       <c r="N24" t="n">
-        <v>0.033918704838</v>
+        <v>0.04797364771366119</v>
       </c>
       <c r="O24" t="n">
-        <v>0.034284174442</v>
+        <v>0.0480138324201107</v>
       </c>
       <c r="P24" t="n">
-        <v>0.046417050064</v>
+        <v>0.04369455575942993</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.036206543446</v>
+        <v>0.04674158245325089</v>
       </c>
       <c r="R24" t="n">
-        <v>0.037712410092</v>
+        <v>0.0511605478823185</v>
       </c>
       <c r="S24" t="n">
-        <v>0.061908073723</v>
+        <v>0.04456166550517082</v>
       </c>
       <c r="T24" t="n">
-        <v>0.048441808671</v>
+        <v>0.02812404558062553</v>
       </c>
       <c r="U24" t="n">
-        <v>0.060786988586</v>
+        <v>0.03979372605681419</v>
       </c>
       <c r="V24" t="n">
-        <v>0.059574246407</v>
+        <v>0.03736068680882454</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.000297897961</v>
+        <v>0.04015135392546654</v>
       </c>
       <c r="X24" t="n">
-        <v>0.01719455421</v>
+        <v>0.0605272501707077</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.02298627235</v>
+        <v>0.05398964509367943</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.018357690424</v>
+        <v>0.04452743753790855</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.022717259824</v>
+        <v>0.04650046303868294</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.030926017091</v>
+        <v>0.04929256439208984</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.061071455479</v>
+        <v>0.04862866923213005</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.033836595714</v>
+        <v>0.04627778753638268</v>
       </c>
       <c r="AE24" t="n">
-        <v>0.036635257304</v>
+        <v>0.04186327010393143</v>
       </c>
       <c r="AF24" t="n">
-        <v>0.018403859809</v>
+        <v>0.04941359907388687</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.04202207922935486</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.03091031312942505</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.03106052428483963</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.02725236490368843</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.03540640324354172</v>
       </c>
     </row>
     <row r="25">
@@ -2936,94 +3306,109 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.048061408103</v>
+        <v>0.04826566204428673</v>
       </c>
       <c r="D25" t="n">
-        <v>0.080110870302</v>
+        <v>0.0551832988858223</v>
       </c>
       <c r="E25" t="n">
-        <v>0.074406094849</v>
+        <v>0.04952184855937958</v>
       </c>
       <c r="F25" t="n">
-        <v>0.076146617532</v>
+        <v>0.05047402903437614</v>
       </c>
       <c r="G25" t="n">
-        <v>0.073782384396</v>
+        <v>0.04856069758534431</v>
       </c>
       <c r="H25" t="n">
-        <v>0.054518319666</v>
+        <v>0.05223353579640388</v>
       </c>
       <c r="I25" t="n">
-        <v>0.059145074338</v>
+        <v>0.04962974786758423</v>
       </c>
       <c r="J25" t="n">
-        <v>0.053703539073</v>
+        <v>0.05855666473507881</v>
       </c>
       <c r="K25" t="n">
-        <v>0.050927024335</v>
+        <v>0.04947185143828392</v>
       </c>
       <c r="L25" t="n">
-        <v>0.048863533884</v>
+        <v>0.03971686214208603</v>
       </c>
       <c r="M25" t="n">
-        <v>0.06542471051199999</v>
+        <v>0.05197431147098541</v>
       </c>
       <c r="N25" t="n">
-        <v>0.062674351037</v>
+        <v>0.0569668672978878</v>
       </c>
       <c r="O25" t="n">
-        <v>0.067217692733</v>
+        <v>0.05261522531509399</v>
       </c>
       <c r="P25" t="n">
-        <v>0.075413122773</v>
+        <v>0.05039149522781372</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.064392484725</v>
+        <v>0.05394944548606873</v>
       </c>
       <c r="R25" t="n">
-        <v>0.048055287451</v>
+        <v>0.05452247709035873</v>
       </c>
       <c r="S25" t="n">
-        <v>0.074437133968</v>
+        <v>0.05784765258431435</v>
       </c>
       <c r="T25" t="n">
-        <v>0.071911685169</v>
+        <v>0.042006965726614</v>
       </c>
       <c r="U25" t="n">
-        <v>0.072302930057</v>
+        <v>0.05382465943694115</v>
       </c>
       <c r="V25" t="n">
-        <v>0.074422739446</v>
+        <v>0.05268517136573792</v>
       </c>
       <c r="W25" t="n">
-        <v>0.025685619563</v>
+        <v>0.0552026592195034</v>
       </c>
       <c r="X25" t="n">
-        <v>0.049759771675</v>
+        <v>0.06384462118148804</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.056888498366</v>
+        <v>0.06130886450409889</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.051179997623</v>
+        <v>0.05780307948589325</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.051960207522</v>
+        <v>0.06752312183380127</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.051942355931</v>
+        <v>0.06940162181854248</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.075724557042</v>
+        <v>0.06237605586647987</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.064018674195</v>
+        <v>0.06820330768823624</v>
       </c>
       <c r="AE25" t="n">
-        <v>0.075087249279</v>
+        <v>0.05204116180539131</v>
       </c>
       <c r="AF25" t="n">
-        <v>0.041221581399</v>
+        <v>0.04569064825773239</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.05054682493209839</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.04351292178034782</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.04605074971914291</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.03764265775680542</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.05389054864645004</v>
       </c>
     </row>
     <row r="26">
@@ -3038,94 +3423,109 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.057850822806</v>
+        <v>0.05000649392604828</v>
       </c>
       <c r="D26" t="n">
-        <v>0.06680960953200001</v>
+        <v>0.07359118014574051</v>
       </c>
       <c r="E26" t="n">
-        <v>0.059420518577</v>
+        <v>0.05476704984903336</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06485228985499999</v>
+        <v>0.05469625815749168</v>
       </c>
       <c r="G26" t="n">
-        <v>0.056068625301</v>
+        <v>0.04922712594270706</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07801382988699999</v>
+        <v>0.05368999019265175</v>
       </c>
       <c r="I26" t="n">
-        <v>0.050825517625</v>
+        <v>0.05473167076706886</v>
       </c>
       <c r="J26" t="n">
-        <v>0.050268121064</v>
+        <v>0.06005674973130226</v>
       </c>
       <c r="K26" t="n">
-        <v>0.041178215295</v>
+        <v>0.0595388300716877</v>
       </c>
       <c r="L26" t="n">
-        <v>0.034958362579</v>
+        <v>0.02519308030605316</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07308468967700001</v>
+        <v>0.04903901368379593</v>
       </c>
       <c r="N26" t="n">
-        <v>0.057397261262</v>
+        <v>0.05097923055291176</v>
       </c>
       <c r="O26" t="n">
-        <v>0.059953860939</v>
+        <v>0.05177783966064453</v>
       </c>
       <c r="P26" t="n">
-        <v>0.06290929019499999</v>
+        <v>0.04436479508876801</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.058737769723</v>
+        <v>0.06677059829235077</v>
       </c>
       <c r="R26" t="n">
-        <v>0.062269780785</v>
+        <v>0.06155399233102798</v>
       </c>
       <c r="S26" t="n">
-        <v>0.07407996058499999</v>
+        <v>0.0708090215921402</v>
       </c>
       <c r="T26" t="n">
-        <v>0.062582015991</v>
+        <v>0.04017499089241028</v>
       </c>
       <c r="U26" t="n">
-        <v>0.073291778564</v>
+        <v>0.05578122287988663</v>
       </c>
       <c r="V26" t="n">
-        <v>0.07246249914199999</v>
+        <v>0.05495279654860497</v>
       </c>
       <c r="W26" t="n">
-        <v>0.049614679068</v>
+        <v>0.06082580611109734</v>
       </c>
       <c r="X26" t="n">
-        <v>0.053516343236</v>
+        <v>0.09174702316522598</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.051932804286</v>
+        <v>0.07854355126619339</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.046555165201</v>
+        <v>0.06102408468723297</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.044166915119</v>
+        <v>0.06798176467418671</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.049438696355</v>
+        <v>0.06987257301807404</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.07396230846600001</v>
+        <v>0.06180104985833168</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.057392574847</v>
+        <v>0.06559810042381287</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.057166770101</v>
+        <v>0.04440190643072128</v>
       </c>
       <c r="AF26" t="n">
-        <v>0.030526483431</v>
+        <v>0.04311871528625488</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.04710755497217178</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.031830795109272</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.02477702125906944</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.02349197119474411</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.03739577904343605</v>
       </c>
     </row>
     <row r="27">
@@ -3140,94 +3540,109 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.054791707546</v>
+        <v>0.06955324858427048</v>
       </c>
       <c r="D27" t="n">
-        <v>0.069639436901</v>
+        <v>0.07682912051677704</v>
       </c>
       <c r="E27" t="n">
-        <v>0.065964639187</v>
+        <v>0.06854948401451111</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06882340461</v>
+        <v>0.0724233090877533</v>
       </c>
       <c r="G27" t="n">
-        <v>0.06642933189899999</v>
+        <v>0.07088075578212738</v>
       </c>
       <c r="H27" t="n">
-        <v>0.066947318614</v>
+        <v>0.07398726046085358</v>
       </c>
       <c r="I27" t="n">
-        <v>0.066181942821</v>
+        <v>0.07664918154478073</v>
       </c>
       <c r="J27" t="n">
-        <v>0.059603448957</v>
+        <v>0.05027268081903458</v>
       </c>
       <c r="K27" t="n">
-        <v>0.054843902588</v>
+        <v>0.04784907400608063</v>
       </c>
       <c r="L27" t="n">
-        <v>0.049228638411</v>
+        <v>0.03583376482129097</v>
       </c>
       <c r="M27" t="n">
-        <v>0.071978241205</v>
+        <v>0.04672899842262268</v>
       </c>
       <c r="N27" t="n">
-        <v>0.06926641613200001</v>
+        <v>0.05015699565410614</v>
       </c>
       <c r="O27" t="n">
-        <v>0.070270903409</v>
+        <v>0.05395087972283363</v>
       </c>
       <c r="P27" t="n">
-        <v>0.080853149295</v>
+        <v>0.04359778016805649</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.06964281201399999</v>
+        <v>0.0739794597029686</v>
       </c>
       <c r="R27" t="n">
-        <v>0.043703407049</v>
+        <v>0.06399229168891907</v>
       </c>
       <c r="S27" t="n">
-        <v>0.06738623976700001</v>
+        <v>0.08361496776342392</v>
       </c>
       <c r="T27" t="n">
-        <v>0.056647434831</v>
+        <v>0.05976550281047821</v>
       </c>
       <c r="U27" t="n">
-        <v>0.06524515896999999</v>
+        <v>0.07426811009645462</v>
       </c>
       <c r="V27" t="n">
-        <v>0.064142115414</v>
+        <v>0.07286183536052704</v>
       </c>
       <c r="W27" t="n">
-        <v>0.025476112962</v>
+        <v>0.07262106239795685</v>
       </c>
       <c r="X27" t="n">
-        <v>0.048044323921</v>
+        <v>0.06945637613534927</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.053957350552</v>
+        <v>0.06613072752952576</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.053692046553</v>
+        <v>0.07014811038970947</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.054642036557</v>
+        <v>0.07353036850690842</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.062670819461</v>
+        <v>0.08385591953992844</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.06560555100400001</v>
+        <v>0.07916745543479919</v>
       </c>
       <c r="AD27" t="n">
-        <v>0.070779196918</v>
+        <v>0.08016896992921829</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.06463714689</v>
+        <v>0.0628155916929245</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.051322028041</v>
+        <v>0.05722248926758766</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.05795014649629593</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.05751412734389305</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0.05616754293441772</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.05530647560954094</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.06996747851371765</v>
       </c>
     </row>
     <row r="28">
@@ -3242,94 +3657,109 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.049388289452</v>
+        <v>0.05272512137889862</v>
       </c>
       <c r="D28" t="n">
-        <v>0.095338821411</v>
+        <v>0.05912595987319946</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08154740184500001</v>
+        <v>0.05536831542849541</v>
       </c>
       <c r="F28" t="n">
-        <v>0.091991893947</v>
+        <v>0.05111376941204071</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08630643785</v>
+        <v>0.05024252086877823</v>
       </c>
       <c r="H28" t="n">
-        <v>0.053812347353</v>
+        <v>0.05338625982403755</v>
       </c>
       <c r="I28" t="n">
-        <v>0.083205193281</v>
+        <v>0.0517323911190033</v>
       </c>
       <c r="J28" t="n">
-        <v>0.075756147504</v>
+        <v>0.04224924743175507</v>
       </c>
       <c r="K28" t="n">
-        <v>0.070043295622</v>
+        <v>0.04802244156599045</v>
       </c>
       <c r="L28" t="n">
-        <v>0.06914619356399999</v>
+        <v>0.01654486916959286</v>
       </c>
       <c r="M28" t="n">
-        <v>0.065018609166</v>
+        <v>0.03088679909706116</v>
       </c>
       <c r="N28" t="n">
-        <v>0.039935976267</v>
+        <v>0.03396809473633766</v>
       </c>
       <c r="O28" t="n">
-        <v>0.04147721082</v>
+        <v>0.03458611667156219</v>
       </c>
       <c r="P28" t="n">
-        <v>0.049019057304</v>
+        <v>0.03048966638743877</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.038900975138</v>
+        <v>0.04492673277854919</v>
       </c>
       <c r="R28" t="n">
-        <v>0.003841152415</v>
+        <v>0.04661384224891663</v>
       </c>
       <c r="S28" t="n">
-        <v>0.050259053707</v>
+        <v>0.04237988218665123</v>
       </c>
       <c r="T28" t="n">
-        <v>0.044161379337</v>
+        <v>0.02180228941142559</v>
       </c>
       <c r="U28" t="n">
-        <v>0.050943430513</v>
+        <v>0.04056739807128906</v>
       </c>
       <c r="V28" t="n">
-        <v>0.056990955025</v>
+        <v>0.03519607335329056</v>
       </c>
       <c r="W28" t="n">
-        <v>0.00284392247</v>
+        <v>0.0407552495598793</v>
       </c>
       <c r="X28" t="n">
-        <v>0.058032985777</v>
+        <v>0.09287616610527039</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.059948284179</v>
+        <v>0.09709848463535309</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.065379209816</v>
+        <v>0.08019127696752548</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.060695417225</v>
+        <v>0.09510127454996109</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.060355950147</v>
+        <v>0.09929054975509644</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.057929508388</v>
+        <v>0.08518242835998535</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.035636443645</v>
+        <v>0.09720978140830994</v>
       </c>
       <c r="AE28" t="n">
-        <v>0.09377610683400001</v>
+        <v>0.07435066998004913</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.064009204507</v>
+        <v>0.07072858512401581</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0.07491867989301682</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0.07719902694225311</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.06778857111930847</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.06201527640223503</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.07515133917331696</v>
       </c>
     </row>
     <row r="29">
@@ -3344,94 +3774,109 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.034922361374</v>
+        <v>0.05030740797519684</v>
       </c>
       <c r="D29" t="n">
-        <v>0.053069807589</v>
+        <v>0.05170607566833496</v>
       </c>
       <c r="E29" t="n">
-        <v>0.041863840073</v>
+        <v>0.05117639526724815</v>
       </c>
       <c r="F29" t="n">
-        <v>0.047104418278</v>
+        <v>0.052326750010252</v>
       </c>
       <c r="G29" t="n">
-        <v>0.041550997645</v>
+        <v>0.05241546407341957</v>
       </c>
       <c r="H29" t="n">
-        <v>0.043245192617</v>
+        <v>0.05560751259326935</v>
       </c>
       <c r="I29" t="n">
-        <v>0.024456899613</v>
+        <v>0.05478610098361969</v>
       </c>
       <c r="J29" t="n">
-        <v>0.014439032413</v>
+        <v>0.04338039085268974</v>
       </c>
       <c r="K29" t="n">
-        <v>0.009342529811</v>
+        <v>0.03288223966956139</v>
       </c>
       <c r="L29" t="n">
-        <v>0.008863904513000001</v>
+        <v>0.02270241640508175</v>
       </c>
       <c r="M29" t="n">
-        <v>0.044375129044</v>
+        <v>0.04304944351315498</v>
       </c>
       <c r="N29" t="n">
-        <v>0.03310688585</v>
+        <v>0.0454886369407177</v>
       </c>
       <c r="O29" t="n">
-        <v>0.035256929696</v>
+        <v>0.04491041600704193</v>
       </c>
       <c r="P29" t="n">
-        <v>0.044009320438</v>
+        <v>0.03854506462812424</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.03227788955</v>
+        <v>0.04542302712798119</v>
       </c>
       <c r="R29" t="n">
-        <v>0.032590147108</v>
+        <v>0.04585685580968857</v>
       </c>
       <c r="S29" t="n">
-        <v>0.051093738526</v>
+        <v>0.05783857405185699</v>
       </c>
       <c r="T29" t="n">
-        <v>0.036877837032</v>
+        <v>0.03745890036225319</v>
       </c>
       <c r="U29" t="n">
-        <v>0.050124932081</v>
+        <v>0.05145478621125221</v>
       </c>
       <c r="V29" t="n">
-        <v>0.047834679484</v>
+        <v>0.0455099381506443</v>
       </c>
       <c r="W29" t="n">
-        <v>0.026061210781</v>
+        <v>0.05111157149076462</v>
       </c>
       <c r="X29" t="n">
-        <v>0.027946021408</v>
+        <v>0.05671887844800949</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.027815189213</v>
+        <v>0.04943307489156723</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.028600096703</v>
+        <v>0.05441883951425552</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.033042203635</v>
+        <v>0.06220551580190659</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.029501985759</v>
+        <v>0.06995721161365509</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.047561466694</v>
+        <v>0.05696769803762436</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.027129445225</v>
+        <v>0.06642524152994156</v>
       </c>
       <c r="AE29" t="n">
-        <v>0.037962727249</v>
+        <v>0.03025035560131073</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.000190636143</v>
+        <v>0.04119726270437241</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.03622952476143837</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.03411661833524704</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.02846258878707886</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.03131434321403503</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.04633684828877449</v>
       </c>
     </row>
     <row r="30">
@@ -3446,94 +3891,109 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.03140360862</v>
+        <v>0.06550422310829163</v>
       </c>
       <c r="D30" t="n">
-        <v>0.072468906641</v>
+        <v>0.07663615792989731</v>
       </c>
       <c r="E30" t="n">
-        <v>0.064733758569</v>
+        <v>0.07460344582796097</v>
       </c>
       <c r="F30" t="n">
-        <v>0.073517411947</v>
+        <v>0.06595092266798019</v>
       </c>
       <c r="G30" t="n">
-        <v>0.06816735863700001</v>
+        <v>0.06705711781978607</v>
       </c>
       <c r="H30" t="n">
-        <v>0.067021839321</v>
+        <v>0.07095231115818024</v>
       </c>
       <c r="I30" t="n">
-        <v>0.049023643136</v>
+        <v>0.06832599639892578</v>
       </c>
       <c r="J30" t="n">
-        <v>0.048486437649</v>
+        <v>0.04364100843667984</v>
       </c>
       <c r="K30" t="n">
-        <v>0.044130068272</v>
+        <v>0.0497068278491497</v>
       </c>
       <c r="L30" t="n">
-        <v>0.041503369808</v>
+        <v>0.0330769270658493</v>
       </c>
       <c r="M30" t="n">
-        <v>0.053280904889</v>
+        <v>0.04402192682027817</v>
       </c>
       <c r="N30" t="n">
-        <v>0.060159031302</v>
+        <v>0.04669540375471115</v>
       </c>
       <c r="O30" t="n">
-        <v>0.05852272734</v>
+        <v>0.04455361142754555</v>
       </c>
       <c r="P30" t="n">
-        <v>0.073853783309</v>
+        <v>0.0382586270570755</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.059987477958</v>
+        <v>0.06654046475887299</v>
       </c>
       <c r="R30" t="n">
-        <v>0.022431809455</v>
+        <v>0.06909743696451187</v>
       </c>
       <c r="S30" t="n">
-        <v>0.058791447431</v>
+        <v>0.07132750749588013</v>
       </c>
       <c r="T30" t="n">
-        <v>0.048091806471</v>
+        <v>0.05028752982616425</v>
       </c>
       <c r="U30" t="n">
-        <v>0.058779463172</v>
+        <v>0.06422001868486404</v>
       </c>
       <c r="V30" t="n">
-        <v>0.057891082019</v>
+        <v>0.05662839859724045</v>
       </c>
       <c r="W30" t="n">
-        <v>0.029438283294</v>
+        <v>0.06558384746313095</v>
       </c>
       <c r="X30" t="n">
-        <v>0.044136986136</v>
+        <v>0.07088280469179153</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.043953891844</v>
+        <v>0.06962337344884872</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.044743418694</v>
+        <v>0.06165676936507225</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.050800830126</v>
+        <v>0.06840858608484268</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.052425779402</v>
+        <v>0.07325921207666397</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.059937462211</v>
+        <v>0.0562620498239994</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.057351261377</v>
+        <v>0.06949124485254288</v>
       </c>
       <c r="AE30" t="n">
-        <v>0.067960835993</v>
+        <v>0.04956619814038277</v>
       </c>
       <c r="AF30" t="n">
-        <v>0.036384921521</v>
+        <v>0.06089217215776443</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0.05635891854763031</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0.04923520609736443</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.04442851990461349</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.04405645281076431</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.05559443682432175</v>
       </c>
     </row>
     <row r="31">
@@ -3548,94 +4008,109 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.029939942062</v>
+        <v>0.05392454564571381</v>
       </c>
       <c r="D31" t="n">
-        <v>0.058686707169</v>
+        <v>0.06563054770231247</v>
       </c>
       <c r="E31" t="n">
-        <v>0.057446122169</v>
+        <v>0.04628414660692215</v>
       </c>
       <c r="F31" t="n">
-        <v>0.056467909366</v>
+        <v>0.05872543156147003</v>
       </c>
       <c r="G31" t="n">
-        <v>0.054478548467</v>
+        <v>0.05221410840749741</v>
       </c>
       <c r="H31" t="n">
-        <v>0.067430242896</v>
+        <v>0.056552954018116</v>
       </c>
       <c r="I31" t="n">
-        <v>0.046210415661</v>
+        <v>0.05515272170305252</v>
       </c>
       <c r="J31" t="n">
-        <v>0.041026107967</v>
+        <v>0.05455406382679939</v>
       </c>
       <c r="K31" t="n">
-        <v>0.032015901059</v>
+        <v>0.03490887209773064</v>
       </c>
       <c r="L31" t="n">
-        <v>0.026158958673</v>
+        <v>0.04408080130815506</v>
       </c>
       <c r="M31" t="n">
-        <v>0.039574868977</v>
+        <v>0.04842856526374817</v>
       </c>
       <c r="N31" t="n">
-        <v>0.046242430806</v>
+        <v>0.048700962215662</v>
       </c>
       <c r="O31" t="n">
-        <v>0.053737428039</v>
+        <v>0.05264898762106895</v>
       </c>
       <c r="P31" t="n">
-        <v>0.057561330497</v>
+        <v>0.04551678895950317</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.048767901957</v>
+        <v>0.05542933568358421</v>
       </c>
       <c r="R31" t="n">
-        <v>0.03727080673</v>
+        <v>0.03809530660510063</v>
       </c>
       <c r="S31" t="n">
-        <v>0.06671082228399999</v>
+        <v>0.06935083866119385</v>
       </c>
       <c r="T31" t="n">
-        <v>0.06770935654599999</v>
+        <v>0.04257263615727425</v>
       </c>
       <c r="U31" t="n">
-        <v>0.063514441252</v>
+        <v>0.05414905399084091</v>
       </c>
       <c r="V31" t="n">
-        <v>0.065200902522</v>
+        <v>0.0524538978934288</v>
       </c>
       <c r="W31" t="n">
-        <v>0.012516829185</v>
+        <v>0.05622179061174393</v>
       </c>
       <c r="X31" t="n">
-        <v>0.042465876788</v>
+        <v>0.06237515434622765</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.05356779322</v>
+        <v>0.03827834129333496</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.046511128545</v>
+        <v>0.05655703693628311</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.046579893678</v>
+        <v>0.06152531504631042</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.048684149981</v>
+        <v>0.06834360957145691</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.065549023449</v>
+        <v>0.05729365348815918</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.046701401472</v>
+        <v>0.06431315839290619</v>
       </c>
       <c r="AE31" t="n">
-        <v>0.052809216082</v>
+        <v>0.03657581657171249</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.025185510516</v>
+        <v>0.02877967618405819</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.04229536652565002</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.03334802016615868</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.02858036383986473</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.0329897403717041</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.0388626754283905</v>
       </c>
     </row>
     <row r="32">
@@ -3650,94 +4125,109 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.040096357465</v>
+        <v>0.06281819194555283</v>
       </c>
       <c r="D32" t="n">
-        <v>0.068764232099</v>
+        <v>0.06308107078075409</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06505719572300001</v>
+        <v>0.06917185336351395</v>
       </c>
       <c r="F32" t="n">
-        <v>0.074611708522</v>
+        <v>0.05987737327814102</v>
       </c>
       <c r="G32" t="n">
-        <v>0.063800439239</v>
+        <v>0.05989274010062218</v>
       </c>
       <c r="H32" t="n">
-        <v>0.060519058257</v>
+        <v>0.06472484767436981</v>
       </c>
       <c r="I32" t="n">
-        <v>0.046442694962</v>
+        <v>0.06006946414709091</v>
       </c>
       <c r="J32" t="n">
-        <v>0.046999931335</v>
+        <v>0.03987174853682518</v>
       </c>
       <c r="K32" t="n">
-        <v>0.03314248845</v>
+        <v>0.04237035289406776</v>
       </c>
       <c r="L32" t="n">
-        <v>0.028755091131</v>
+        <v>0.03746704757213593</v>
       </c>
       <c r="M32" t="n">
-        <v>0.058921478689</v>
+        <v>0.04367435351014137</v>
       </c>
       <c r="N32" t="n">
-        <v>0.067600727081</v>
+        <v>0.04899676144123077</v>
       </c>
       <c r="O32" t="n">
-        <v>0.07631017267699999</v>
+        <v>0.04201913997530937</v>
       </c>
       <c r="P32" t="n">
-        <v>0.09238904714600001</v>
+        <v>0.03964903205633163</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.07033203542200001</v>
+        <v>0.06114110723137856</v>
       </c>
       <c r="R32" t="n">
-        <v>0.028587188572</v>
+        <v>0.06911284476518631</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06915204972</v>
+        <v>0.07046868652105331</v>
       </c>
       <c r="T32" t="n">
-        <v>0.066168494523</v>
+        <v>0.05042501538991928</v>
       </c>
       <c r="U32" t="n">
-        <v>0.069714330137</v>
+        <v>0.06756218522787094</v>
       </c>
       <c r="V32" t="n">
-        <v>0.06824807822700001</v>
+        <v>0.05800524726510048</v>
       </c>
       <c r="W32" t="n">
-        <v>0.026852671057</v>
+        <v>0.06454640626907349</v>
       </c>
       <c r="X32" t="n">
-        <v>0.061778675765</v>
+        <v>0.08083102852106094</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.06512042135</v>
+        <v>0.08437469601631165</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.070738434792</v>
+        <v>0.06575970351696014</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.068400666118</v>
+        <v>0.07786305248737335</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.068081751466</v>
+        <v>0.09109080582857132</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.067214690149</v>
+        <v>0.07437118887901306</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.06357430666699999</v>
+        <v>0.08486843109130859</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.061284862459</v>
+        <v>0.04009586572647095</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.019879758358</v>
+        <v>0.04081482067704201</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.0504286028444767</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.03955774009227753</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.0401327833533287</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.03885652869939804</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.05465345829725266</v>
       </c>
     </row>
     <row r="33">
@@ -3752,94 +4242,109 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.022944934666</v>
+        <v>0.05337385088205338</v>
       </c>
       <c r="D33" t="n">
-        <v>0.041021402925</v>
+        <v>0.06589636951684952</v>
       </c>
       <c r="E33" t="n">
-        <v>0.029910024256</v>
+        <v>0.05890563130378723</v>
       </c>
       <c r="F33" t="n">
-        <v>0.039654109627</v>
+        <v>0.05180725082755089</v>
       </c>
       <c r="G33" t="n">
-        <v>0.034458678216</v>
+        <v>0.05106687173247337</v>
       </c>
       <c r="H33" t="n">
-        <v>0.058430124074</v>
+        <v>0.05585850030183792</v>
       </c>
       <c r="I33" t="n">
-        <v>0.025308612734</v>
+        <v>0.0504995658993721</v>
       </c>
       <c r="J33" t="n">
-        <v>0.017281442881</v>
+        <v>0.04448750242590904</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01332052052</v>
+        <v>0.03823544085025787</v>
       </c>
       <c r="L33" t="n">
-        <v>0.008062163367999999</v>
+        <v>0.02518733590841293</v>
       </c>
       <c r="M33" t="n">
-        <v>0.047369219363</v>
+        <v>0.03676076978445053</v>
       </c>
       <c r="N33" t="n">
-        <v>0.039160557091</v>
+        <v>0.0396525040268898</v>
       </c>
       <c r="O33" t="n">
-        <v>0.04354378581</v>
+        <v>0.03957460075616837</v>
       </c>
       <c r="P33" t="n">
-        <v>0.057173833251</v>
+        <v>0.03141916915774345</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.039304371923</v>
+        <v>0.04837159812450409</v>
       </c>
       <c r="R33" t="n">
-        <v>0.040863394737</v>
+        <v>0.05153080821037292</v>
       </c>
       <c r="S33" t="n">
-        <v>0.058707047254</v>
+        <v>0.05734161660075188</v>
       </c>
       <c r="T33" t="n">
-        <v>0.046705305576</v>
+        <v>0.0343368798494339</v>
       </c>
       <c r="U33" t="n">
-        <v>0.05451932922</v>
+        <v>0.04810294881463051</v>
       </c>
       <c r="V33" t="n">
-        <v>0.054249949753</v>
+        <v>0.03788188099861145</v>
       </c>
       <c r="W33" t="n">
-        <v>0.013012966141</v>
+        <v>0.04995287954807281</v>
       </c>
       <c r="X33" t="n">
-        <v>0.029408589005</v>
+        <v>0.05436345562338829</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.026645563543</v>
+        <v>0.04302314296364784</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.022682657465</v>
+        <v>0.04118307679891586</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.028301442042</v>
+        <v>0.04730435833334923</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.032630566508</v>
+        <v>0.05491308867931366</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.053807038814</v>
+        <v>0.0324091762304306</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.036113366485</v>
+        <v>0.05163108184933662</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.029224000871</v>
+        <v>0.035968367010355</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.002132558264</v>
+        <v>0.03963729739189148</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.03265569731593132</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.02882399782538414</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.02126632072031498</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.01985685527324677</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0.04015500098466873</v>
       </c>
     </row>
     <row r="34">
@@ -3854,94 +4359,109 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.025221366435</v>
+        <v>0.06723550707101822</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08393188566</v>
+        <v>0.08447358012199402</v>
       </c>
       <c r="E34" t="n">
-        <v>0.076506234705</v>
+        <v>0.06947682797908783</v>
       </c>
       <c r="F34" t="n">
-        <v>0.078955024481</v>
+        <v>0.07050170004367828</v>
       </c>
       <c r="G34" t="n">
-        <v>0.078426592052</v>
+        <v>0.06520528346300125</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0452234447</v>
+        <v>0.0684739276766777</v>
       </c>
       <c r="I34" t="n">
-        <v>0.063517846167</v>
+        <v>0.0722140297293663</v>
       </c>
       <c r="J34" t="n">
-        <v>0.052663806826</v>
+        <v>0.07481256872415543</v>
       </c>
       <c r="K34" t="n">
-        <v>0.041303738952</v>
+        <v>0.04802412167191505</v>
       </c>
       <c r="L34" t="n">
-        <v>0.041283488274</v>
+        <v>0.05257072299718857</v>
       </c>
       <c r="M34" t="n">
-        <v>0.040737722069</v>
+        <v>0.05771208927035332</v>
       </c>
       <c r="N34" t="n">
-        <v>0.063996113837</v>
+        <v>0.05897429212927818</v>
       </c>
       <c r="O34" t="n">
-        <v>0.066229060292</v>
+        <v>0.06126780807971954</v>
       </c>
       <c r="P34" t="n">
-        <v>0.071790471673</v>
+        <v>0.05338516086339951</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.066262423992</v>
+        <v>0.07754592597484589</v>
       </c>
       <c r="R34" t="n">
-        <v>0.017832739279</v>
+        <v>0.06648261845111847</v>
       </c>
       <c r="S34" t="n">
-        <v>0.074001915753</v>
+        <v>0.07520697265863419</v>
       </c>
       <c r="T34" t="n">
-        <v>0.071771003306</v>
+        <v>0.0545501708984375</v>
       </c>
       <c r="U34" t="n">
-        <v>0.072130195796</v>
+        <v>0.06637229770421982</v>
       </c>
       <c r="V34" t="n">
-        <v>0.071477264166</v>
+        <v>0.06376670300960541</v>
       </c>
       <c r="W34" t="n">
-        <v>-0.007720299531</v>
+        <v>0.06917974352836609</v>
       </c>
       <c r="X34" t="n">
-        <v>0.052825365216</v>
+        <v>0.09273752570152283</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.048423949629</v>
+        <v>0.06569233536720276</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.041341073811</v>
+        <v>0.07674665004014969</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.04632435739</v>
+        <v>0.07877573370933533</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.054380837828</v>
+        <v>0.07975784689188004</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.073621332645</v>
+        <v>0.07603807747364044</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.062548667192</v>
+        <v>0.08184973895549774</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.076107114553</v>
+        <v>0.06234083697199821</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.034458853304</v>
+        <v>0.05751042813062668</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.07046541571617126</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.05364334583282471</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0.04784175008535385</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0.05472103506326675</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0.06183505430817604</v>
       </c>
     </row>
     <row r="35">
@@ -3956,94 +4476,109 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.027619164437</v>
+        <v>0.04691659286618233</v>
       </c>
       <c r="D35" t="n">
-        <v>0.049635957927</v>
+        <v>0.04458145797252655</v>
       </c>
       <c r="E35" t="n">
-        <v>0.050190627575</v>
+        <v>0.04392055422067642</v>
       </c>
       <c r="F35" t="n">
-        <v>0.049940019846</v>
+        <v>0.04957176744937897</v>
       </c>
       <c r="G35" t="n">
-        <v>0.047404170036</v>
+        <v>0.04540012404322624</v>
       </c>
       <c r="H35" t="n">
-        <v>0.058666024357</v>
+        <v>0.0498553030192852</v>
       </c>
       <c r="I35" t="n">
-        <v>0.040633205324</v>
+        <v>0.04948322102427483</v>
       </c>
       <c r="J35" t="n">
-        <v>0.034634474665</v>
+        <v>0.03451643884181976</v>
       </c>
       <c r="K35" t="n">
-        <v>0.030436748639</v>
+        <v>0.02090331539511681</v>
       </c>
       <c r="L35" t="n">
-        <v>0.025689987466</v>
+        <v>0.02268250845372677</v>
       </c>
       <c r="M35" t="n">
-        <v>0.040012560785</v>
+        <v>0.03435846418142319</v>
       </c>
       <c r="N35" t="n">
-        <v>0.037104405463</v>
+        <v>0.03989173471927643</v>
       </c>
       <c r="O35" t="n">
-        <v>0.049934476614</v>
+        <v>0.03783883154392242</v>
       </c>
       <c r="P35" t="n">
-        <v>0.054471313953</v>
+        <v>0.03177066147327423</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.03610759601</v>
+        <v>0.03869980201125145</v>
       </c>
       <c r="R35" t="n">
-        <v>0.029165357351</v>
+        <v>0.03113625571131706</v>
       </c>
       <c r="S35" t="n">
-        <v>0.064841762185</v>
+        <v>0.06004708260297775</v>
       </c>
       <c r="T35" t="n">
-        <v>0.06415643543000001</v>
+        <v>0.03455790877342224</v>
       </c>
       <c r="U35" t="n">
-        <v>0.06523052603</v>
+        <v>0.04835702106356621</v>
       </c>
       <c r="V35" t="n">
-        <v>0.065895676613</v>
+        <v>0.04400162398815155</v>
       </c>
       <c r="W35" t="n">
-        <v>0.018135258928</v>
+        <v>0.04805979877710342</v>
       </c>
       <c r="X35" t="n">
-        <v>0.026830965653</v>
+        <v>0.04285093769431114</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.036813985556</v>
+        <v>0.03380603715777397</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.029773712158</v>
+        <v>0.05337763577699661</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.031209796667</v>
+        <v>0.05007654801011086</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.042050197721</v>
+        <v>0.06116365641355515</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.066222041845</v>
+        <v>0.05117367580533028</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.035402260721</v>
+        <v>0.05721697211265564</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.045467801392</v>
+        <v>0.03784672915935516</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.023190774024</v>
+        <v>0.03432870283722878</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.0403432697057724</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.03666682541370392</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0.03558262437582016</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.02245405316352844</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.05005906522274017</v>
       </c>
     </row>
     <row r="36">
@@ -4058,94 +4593,109 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.055931072682</v>
+        <v>0.03592632338404655</v>
       </c>
       <c r="D36" t="n">
-        <v>0.048543322831</v>
+        <v>0.03613488003611565</v>
       </c>
       <c r="E36" t="n">
-        <v>0.044906731695</v>
+        <v>0.03405468538403511</v>
       </c>
       <c r="F36" t="n">
-        <v>0.046586044133</v>
+        <v>0.03623127564787865</v>
       </c>
       <c r="G36" t="n">
-        <v>0.043358847499</v>
+        <v>0.03503390401601791</v>
       </c>
       <c r="H36" t="n">
-        <v>0.051414530724</v>
+        <v>0.033763587474823</v>
       </c>
       <c r="I36" t="n">
-        <v>0.014240102842</v>
+        <v>0.03828983008861542</v>
       </c>
       <c r="J36" t="n">
-        <v>0.018946843222</v>
+        <v>0.03520437702536583</v>
       </c>
       <c r="K36" t="n">
-        <v>0.008289270103000001</v>
+        <v>0.0438293069601059</v>
       </c>
       <c r="L36" t="n">
-        <v>0.004241765011</v>
+        <v>0.04143752902746201</v>
       </c>
       <c r="M36" t="n">
-        <v>0.048416364938</v>
+        <v>0.04909011721611023</v>
       </c>
       <c r="N36" t="n">
-        <v>0.037465557456</v>
+        <v>0.04812346398830414</v>
       </c>
       <c r="O36" t="n">
-        <v>0.040910080075</v>
+        <v>0.04786904901266098</v>
       </c>
       <c r="P36" t="n">
-        <v>0.060494568199</v>
+        <v>0.0485445037484169</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.040240775794</v>
+        <v>0.03959785401821136</v>
       </c>
       <c r="R36" t="n">
-        <v>0.035307187587</v>
+        <v>0.04183712229132652</v>
       </c>
       <c r="S36" t="n">
-        <v>0.046219293028</v>
+        <v>0.03863979876041412</v>
       </c>
       <c r="T36" t="n">
-        <v>0.055746745318</v>
+        <v>0.03088195063173771</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04605922848</v>
+        <v>0.04068132862448692</v>
       </c>
       <c r="V36" t="n">
-        <v>0.048320345581</v>
+        <v>0.042366623878479</v>
       </c>
       <c r="W36" t="n">
-        <v>0.035979233682</v>
+        <v>0.04316111281514168</v>
       </c>
       <c r="X36" t="n">
-        <v>0.024099070579</v>
+        <v>0.04167025908827782</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.036572661251</v>
+        <v>0.05672347545623779</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.024583498016</v>
+        <v>0.04787436127662659</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.027995809913</v>
+        <v>0.04821529239416122</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.033547483385</v>
+        <v>0.05035506188869476</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.048337906599</v>
+        <v>0.0500553660094738</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.035772077739</v>
+        <v>0.04864181950688362</v>
       </c>
       <c r="AE36" t="n">
-        <v>0.039225619286</v>
+        <v>0.01385573297739029</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.001372442115</v>
+        <v>0.02589209750294685</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.03392768651247025</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.01809586584568024</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.01253748964518309</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0.01593911647796631</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.01801791973412037</v>
       </c>
     </row>
     <row r="37">
@@ -4160,94 +4710,109 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.06736562401100001</v>
+        <v>0.05858859419822693</v>
       </c>
       <c r="D37" t="n">
-        <v>0.081187129021</v>
+        <v>0.07014666497707367</v>
       </c>
       <c r="E37" t="n">
-        <v>0.075275927782</v>
+        <v>0.06945806741714478</v>
       </c>
       <c r="F37" t="n">
-        <v>0.08944167941800001</v>
+        <v>0.06231798231601715</v>
       </c>
       <c r="G37" t="n">
-        <v>0.081584215164</v>
+        <v>0.05675175413489342</v>
       </c>
       <c r="H37" t="n">
-        <v>0.093827858567</v>
+        <v>0.0622156485915184</v>
       </c>
       <c r="I37" t="n">
-        <v>0.07910604029899999</v>
+        <v>0.0605890154838562</v>
       </c>
       <c r="J37" t="n">
-        <v>0.07604910433299999</v>
+        <v>0.07044026255607605</v>
       </c>
       <c r="K37" t="n">
-        <v>0.072212815285</v>
+        <v>0.08215218782424927</v>
       </c>
       <c r="L37" t="n">
-        <v>0.066120736301</v>
+        <v>0.03736445307731628</v>
       </c>
       <c r="M37" t="n">
-        <v>0.08233255892999999</v>
+        <v>0.07219256460666656</v>
       </c>
       <c r="N37" t="n">
-        <v>0.063757866621</v>
+        <v>0.0754077211022377</v>
       </c>
       <c r="O37" t="n">
-        <v>0.068906068802</v>
+        <v>0.07758411020040512</v>
       </c>
       <c r="P37" t="n">
-        <v>0.084710486233</v>
+        <v>0.07365898787975311</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.063293762505</v>
+        <v>0.05681553855538368</v>
       </c>
       <c r="R37" t="n">
-        <v>0.08262917399399999</v>
+        <v>0.06737814843654633</v>
       </c>
       <c r="S37" t="n">
-        <v>0.098176285625</v>
+        <v>0.07037310302257538</v>
       </c>
       <c r="T37" t="n">
-        <v>0.07708770036699999</v>
+        <v>0.04252923280000687</v>
       </c>
       <c r="U37" t="n">
-        <v>0.095912918448</v>
+        <v>0.05784494802355766</v>
       </c>
       <c r="V37" t="n">
-        <v>0.096342563629</v>
+        <v>0.0541481114923954</v>
       </c>
       <c r="W37" t="n">
-        <v>0.065051294863</v>
+        <v>0.05891954898834229</v>
       </c>
       <c r="X37" t="n">
-        <v>0.070604689419</v>
+        <v>0.09036004543304443</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.06653876602600001</v>
+        <v>0.08835282176733017</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.067698262632</v>
+        <v>0.06850823014974594</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.06507055461400001</v>
+        <v>0.07371657341718674</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.071217373013</v>
+        <v>0.08170850574970245</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.09723940491700001</v>
+        <v>0.07129019498825073</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.060271907598</v>
+        <v>0.08124179393053055</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.080206103623</v>
+        <v>0.06466434150934219</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.057445175946</v>
+        <v>0.06096547842025757</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.06673172861337662</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.05497132614254951</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.04909929633140564</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.04934802651405334</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.06456826627254486</v>
       </c>
     </row>
     <row r="38">
@@ -4262,94 +4827,109 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.031163807958</v>
+        <v>0.03521427884697914</v>
       </c>
       <c r="D38" t="n">
-        <v>0.051919016987</v>
+        <v>0.04115008562803268</v>
       </c>
       <c r="E38" t="n">
-        <v>0.056297913194</v>
+        <v>0.03564885631203651</v>
       </c>
       <c r="F38" t="n">
-        <v>0.051278188825</v>
+        <v>0.0398453027009964</v>
       </c>
       <c r="G38" t="n">
-        <v>0.053425841033</v>
+        <v>0.03653242439031601</v>
       </c>
       <c r="H38" t="n">
-        <v>0.04015705362</v>
+        <v>0.03843244910240173</v>
       </c>
       <c r="I38" t="n">
-        <v>0.035734239966</v>
+        <v>0.04122013971209526</v>
       </c>
       <c r="J38" t="n">
-        <v>0.044366616756</v>
+        <v>0.03775454312562943</v>
       </c>
       <c r="K38" t="n">
-        <v>0.038679186255</v>
+        <v>0.01828669011592865</v>
       </c>
       <c r="L38" t="n">
-        <v>0.03410186246</v>
+        <v>0.03732136636972427</v>
       </c>
       <c r="M38" t="n">
-        <v>0.037183374166</v>
+        <v>0.04100838303565979</v>
       </c>
       <c r="N38" t="n">
-        <v>0.048197694123</v>
+        <v>0.04347125813364983</v>
       </c>
       <c r="O38" t="n">
-        <v>0.054178141057</v>
+        <v>0.04040320590138435</v>
       </c>
       <c r="P38" t="n">
-        <v>0.056998245418</v>
+        <v>0.03803229331970215</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.049241166562</v>
+        <v>0.04725702106952667</v>
       </c>
       <c r="R38" t="n">
-        <v>0.016612164676</v>
+        <v>0.04368552565574646</v>
       </c>
       <c r="S38" t="n">
-        <v>0.042556680739</v>
+        <v>0.05711035057902336</v>
       </c>
       <c r="T38" t="n">
-        <v>0.055057495832</v>
+        <v>0.04258647188544273</v>
       </c>
       <c r="U38" t="n">
-        <v>0.0447579436</v>
+        <v>0.05065766721963882</v>
       </c>
       <c r="V38" t="n">
-        <v>0.047797609121</v>
+        <v>0.05018769577145576</v>
       </c>
       <c r="W38" t="n">
-        <v>0.020445920527</v>
+        <v>0.05255724862217903</v>
       </c>
       <c r="X38" t="n">
-        <v>0.033972986042</v>
+        <v>0.05376243591308594</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.039208497852</v>
+        <v>0.04680357128381729</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.0268628411</v>
+        <v>0.0520704984664917</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.02641459927</v>
+        <v>0.05404688790440559</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.038779966533</v>
+        <v>0.05416034907102585</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.050335437059</v>
+        <v>0.05250496789813042</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.049339026213</v>
+        <v>0.05792746692895889</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.053253524005</v>
+        <v>0.0207001231610775</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.033021487296</v>
+        <v>0.02472181245684624</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.03594353795051575</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.02561352215707302</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.02511447668075562</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0.02154527418315411</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0.02368535287678242</v>
       </c>
     </row>
     <row r="39">
@@ -4364,94 +4944,109 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.04144795239</v>
+        <v>0.04492884129285812</v>
       </c>
       <c r="D39" t="n">
-        <v>0.066646456718</v>
+        <v>0.05623750761151314</v>
       </c>
       <c r="E39" t="n">
-        <v>0.06876751035500001</v>
+        <v>0.05117430165410042</v>
       </c>
       <c r="F39" t="n">
-        <v>0.06442390382300001</v>
+        <v>0.05370310693979263</v>
       </c>
       <c r="G39" t="n">
-        <v>0.057831916958</v>
+        <v>0.04519816860556602</v>
       </c>
       <c r="H39" t="n">
-        <v>0.07620962709200001</v>
+        <v>0.04851559549570084</v>
       </c>
       <c r="I39" t="n">
-        <v>0.067952230573</v>
+        <v>0.04300399497151375</v>
       </c>
       <c r="J39" t="n">
-        <v>0.06573458761000001</v>
+        <v>0.05972298979759216</v>
       </c>
       <c r="K39" t="n">
-        <v>0.057809978724</v>
+        <v>0.05155597627162933</v>
       </c>
       <c r="L39" t="n">
-        <v>0.052970737219</v>
+        <v>0.03521282598376274</v>
       </c>
       <c r="M39" t="n">
-        <v>0.06110760197</v>
+        <v>0.05873191356658936</v>
       </c>
       <c r="N39" t="n">
-        <v>0.068444475532</v>
+        <v>0.06026170402765274</v>
       </c>
       <c r="O39" t="n">
-        <v>0.078396886587</v>
+        <v>0.05565222725272179</v>
       </c>
       <c r="P39" t="n">
-        <v>0.080122351646</v>
+        <v>0.05514344945549965</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.068827420473</v>
+        <v>0.06044922769069672</v>
       </c>
       <c r="R39" t="n">
-        <v>0.058989778161</v>
+        <v>0.06322594732046127</v>
       </c>
       <c r="S39" t="n">
-        <v>0.072278469801</v>
+        <v>0.07540132105350494</v>
       </c>
       <c r="T39" t="n">
-        <v>0.07102259248499999</v>
+        <v>0.05020670592784882</v>
       </c>
       <c r="U39" t="n">
-        <v>0.07500147074500001</v>
+        <v>0.06031636148691177</v>
       </c>
       <c r="V39" t="n">
-        <v>0.07655993849000001</v>
+        <v>0.05713792145252228</v>
       </c>
       <c r="W39" t="n">
-        <v>0.031541898847</v>
+        <v>0.0621730238199234</v>
       </c>
       <c r="X39" t="n">
-        <v>0.034761298448</v>
+        <v>0.06000649183988571</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.050369814038</v>
+        <v>0.05896784737706184</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.032755229622</v>
+        <v>0.07152008265256882</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.040248781443</v>
+        <v>0.05990012735128403</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.038344047964</v>
+        <v>0.06323105096817017</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.077148556709</v>
+        <v>0.0550309494137764</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.066385090351</v>
+        <v>0.0605732649564743</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.055821791291</v>
+        <v>0.06434482336044312</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.045148741454</v>
+        <v>0.05826398357748985</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.06229885295033455</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.04954151436686516</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.04444529116153717</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0.03588684648275375</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.06049870699644089</v>
       </c>
     </row>
     <row r="40">
@@ -4466,94 +5061,109 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.056632462889</v>
+        <v>0.07325917482376099</v>
       </c>
       <c r="D40" t="n">
-        <v>0.073281921446</v>
+        <v>0.08353028446435928</v>
       </c>
       <c r="E40" t="n">
-        <v>0.066593170166</v>
+        <v>0.07728124409914017</v>
       </c>
       <c r="F40" t="n">
-        <v>0.068733386695</v>
+        <v>0.07045258581638336</v>
       </c>
       <c r="G40" t="n">
-        <v>0.067253634334</v>
+        <v>0.07435194402933121</v>
       </c>
       <c r="H40" t="n">
-        <v>0.076653920114</v>
+        <v>0.07652509212493896</v>
       </c>
       <c r="I40" t="n">
-        <v>0.057493757457</v>
+        <v>0.07668337970972061</v>
       </c>
       <c r="J40" t="n">
-        <v>0.058094684035</v>
+        <v>0.07797667384147644</v>
       </c>
       <c r="K40" t="n">
-        <v>0.05392640084</v>
+        <v>0.08405819535255432</v>
       </c>
       <c r="L40" t="n">
-        <v>0.050874639302</v>
+        <v>0.06276074796915054</v>
       </c>
       <c r="M40" t="n">
-        <v>0.07229565084</v>
+        <v>0.07673808187246323</v>
       </c>
       <c r="N40" t="n">
-        <v>0.07058975100500001</v>
+        <v>0.07671131938695908</v>
       </c>
       <c r="O40" t="n">
-        <v>0.071640037</v>
+        <v>0.07762043923139572</v>
       </c>
       <c r="P40" t="n">
-        <v>0.084341570735</v>
+        <v>0.07398081570863724</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.071641862392</v>
+        <v>0.07961010187864304</v>
       </c>
       <c r="R40" t="n">
-        <v>0.070164568722</v>
+        <v>0.08078668266534805</v>
       </c>
       <c r="S40" t="n">
-        <v>0.082383006811</v>
+        <v>0.07827183604240417</v>
       </c>
       <c r="T40" t="n">
-        <v>0.07307433336999999</v>
+        <v>0.0688173845410347</v>
       </c>
       <c r="U40" t="n">
-        <v>0.08097397536000001</v>
+        <v>0.07925125956535339</v>
       </c>
       <c r="V40" t="n">
-        <v>0.081269845366</v>
+        <v>0.07529561966657639</v>
       </c>
       <c r="W40" t="n">
-        <v>0.048107188195</v>
+        <v>0.08104603737592697</v>
       </c>
       <c r="X40" t="n">
-        <v>0.053087800741</v>
+        <v>0.07661852240562439</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.058199547231</v>
+        <v>0.08033069223165512</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.05981682986</v>
+        <v>0.06988269090652466</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.060750685632</v>
+        <v>0.08122027665376663</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.061524201185</v>
+        <v>0.08335573971271515</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.082514762878</v>
+        <v>0.07351285219192505</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.070225976408</v>
+        <v>0.08353091031312943</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.06641554087400001</v>
+        <v>0.0613153874874115</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.043195661157</v>
+        <v>0.06894449144601822</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.06495608389377594</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.06126583740115166</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.05802981555461884</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.06005913019180298</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.06439610570669174</v>
       </c>
     </row>
     <row r="41">
@@ -4568,94 +5178,109 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.021100230515</v>
+        <v>0.05984426662325859</v>
       </c>
       <c r="D41" t="n">
-        <v>0.04937992245</v>
+        <v>0.06838139146566391</v>
       </c>
       <c r="E41" t="n">
-        <v>0.048413105309</v>
+        <v>0.06480716168880463</v>
       </c>
       <c r="F41" t="n">
-        <v>0.048209413886</v>
+        <v>0.06479207426309586</v>
       </c>
       <c r="G41" t="n">
-        <v>0.044987991452</v>
+        <v>0.06233800575137138</v>
       </c>
       <c r="H41" t="n">
-        <v>0.050909597427</v>
+        <v>0.06670211255550385</v>
       </c>
       <c r="I41" t="n">
-        <v>0.041902847588</v>
+        <v>0.05940154194831848</v>
       </c>
       <c r="J41" t="n">
-        <v>0.034962058067</v>
+        <v>0.03887361660599709</v>
       </c>
       <c r="K41" t="n">
-        <v>0.030531559139</v>
+        <v>0.03603507950901985</v>
       </c>
       <c r="L41" t="n">
-        <v>0.027994649485</v>
+        <v>0.02136621996760368</v>
       </c>
       <c r="M41" t="n">
-        <v>0.044208768755</v>
+        <v>0.04730205237865448</v>
       </c>
       <c r="N41" t="n">
-        <v>0.045441292226</v>
+        <v>0.04949582368135452</v>
       </c>
       <c r="O41" t="n">
-        <v>0.050915371627</v>
+        <v>0.04534687474370003</v>
       </c>
       <c r="P41" t="n">
-        <v>0.050423793495</v>
+        <v>0.04224365577101707</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.047589495778</v>
+        <v>0.06067396700382233</v>
       </c>
       <c r="R41" t="n">
-        <v>0.025253780186</v>
+        <v>0.06198116391897202</v>
       </c>
       <c r="S41" t="n">
-        <v>0.050435088575</v>
+        <v>0.07702383399009705</v>
       </c>
       <c r="T41" t="n">
-        <v>0.042002815753</v>
+        <v>0.05961251631379128</v>
       </c>
       <c r="U41" t="n">
-        <v>0.051463339478</v>
+        <v>0.07001520693302155</v>
       </c>
       <c r="V41" t="n">
-        <v>0.049248185009</v>
+        <v>0.06199216842651367</v>
       </c>
       <c r="W41" t="n">
-        <v>0.020514378324</v>
+        <v>0.0706007108092308</v>
       </c>
       <c r="X41" t="n">
-        <v>0.025176400319</v>
+        <v>0.05209964513778687</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.042503252625</v>
+        <v>0.05016416683793068</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.029962521046</v>
+        <v>0.05335898324847221</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.040317822248</v>
+        <v>0.06227832660079002</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.039705082774</v>
+        <v>0.07087883353233337</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.048859283328</v>
+        <v>0.06140422448515892</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.044438563287</v>
+        <v>0.06500259041786194</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.041695252061</v>
+        <v>0.05979070067405701</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.01441936288</v>
+        <v>0.04251592606306076</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0.03852090239524841</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0.04175692051649094</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0.04278629273176193</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0.03151913732290268</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0.06051362305879593</v>
       </c>
     </row>
     <row r="42">
@@ -4670,94 +5295,109 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.064418137074</v>
+        <v>0.07658497989177704</v>
       </c>
       <c r="D42" t="n">
-        <v>0.066130854189</v>
+        <v>0.09209056943655014</v>
       </c>
       <c r="E42" t="n">
-        <v>0.06744267046499999</v>
+        <v>0.08541427552700043</v>
       </c>
       <c r="F42" t="n">
-        <v>0.069038912654</v>
+        <v>0.07944990694522858</v>
       </c>
       <c r="G42" t="n">
-        <v>0.060950353742</v>
+        <v>0.07838320732116699</v>
       </c>
       <c r="H42" t="n">
-        <v>0.08067469298799999</v>
+        <v>0.08242877572774887</v>
       </c>
       <c r="I42" t="n">
-        <v>0.064410366118</v>
+        <v>0.0808723121881485</v>
       </c>
       <c r="J42" t="n">
-        <v>0.061914697289</v>
+        <v>0.07286323606967926</v>
       </c>
       <c r="K42" t="n">
-        <v>0.050811938941</v>
+        <v>0.07948308438062668</v>
       </c>
       <c r="L42" t="n">
-        <v>0.051153164357</v>
+        <v>0.05705827474594116</v>
       </c>
       <c r="M42" t="n">
-        <v>0.076282918453</v>
+        <v>0.06731535494327545</v>
       </c>
       <c r="N42" t="n">
-        <v>0.082720629871</v>
+        <v>0.07021768391132355</v>
       </c>
       <c r="O42" t="n">
-        <v>0.089802227914</v>
+        <v>0.07111369073390961</v>
       </c>
       <c r="P42" t="n">
-        <v>0.102936327457</v>
+        <v>0.06386914849281311</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.08485393226100001</v>
+        <v>0.08723676949739456</v>
       </c>
       <c r="R42" t="n">
-        <v>0.062206074595</v>
+        <v>0.08861973136663437</v>
       </c>
       <c r="S42" t="n">
-        <v>0.082290634513</v>
+        <v>0.09528499096632004</v>
       </c>
       <c r="T42" t="n">
-        <v>0.074925810099</v>
+        <v>0.071212999522686</v>
       </c>
       <c r="U42" t="n">
-        <v>0.07949651777699999</v>
+        <v>0.08399413526058197</v>
       </c>
       <c r="V42" t="n">
-        <v>0.080898337066</v>
+        <v>0.08314310759305954</v>
       </c>
       <c r="W42" t="n">
-        <v>0.041571497917</v>
+        <v>0.08245667070150375</v>
       </c>
       <c r="X42" t="n">
-        <v>0.074143975973</v>
+        <v>0.09415753930807114</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.08129799366</v>
+        <v>0.08982478082180023</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.078753337264</v>
+        <v>0.08315378427505493</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.07718010991800001</v>
+        <v>0.08179962635040283</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.07341960072500001</v>
+        <v>0.091670922935009</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.079641893506</v>
+        <v>0.08901949226856232</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.083863064647</v>
+        <v>0.08423841744661331</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.058382585645</v>
+        <v>0.06832052767276764</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.037137985229</v>
+        <v>0.06952132284641266</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0.0818677544593811</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0.06370949745178223</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0.05830970779061317</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0.06448569893836975</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0.06871190667152405</v>
       </c>
     </row>
     <row r="43">
@@ -4772,94 +5412,109 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.025252485648</v>
+        <v>0.03404926881194115</v>
       </c>
       <c r="D43" t="n">
-        <v>0.045661225915</v>
+        <v>0.03950083255767822</v>
       </c>
       <c r="E43" t="n">
-        <v>0.038137767464</v>
+        <v>0.03931125998497009</v>
       </c>
       <c r="F43" t="n">
-        <v>0.041595071554</v>
+        <v>0.03069565072655678</v>
       </c>
       <c r="G43" t="n">
-        <v>0.038302704692</v>
+        <v>0.03638198599219322</v>
       </c>
       <c r="H43" t="n">
-        <v>0.043612059206</v>
+        <v>0.03982559964060783</v>
       </c>
       <c r="I43" t="n">
-        <v>0.018923424184</v>
+        <v>0.03067334182560444</v>
       </c>
       <c r="J43" t="n">
-        <v>0.021177778021</v>
+        <v>0.01921843178570271</v>
       </c>
       <c r="K43" t="n">
-        <v>0.008573220111</v>
+        <v>0.02368194982409477</v>
       </c>
       <c r="L43" t="n">
-        <v>0.006591323763</v>
+        <v>0.01745856925845146</v>
       </c>
       <c r="M43" t="n">
-        <v>0.033627290279</v>
+        <v>0.01944520883262157</v>
       </c>
       <c r="N43" t="n">
-        <v>0.028287746012</v>
+        <v>0.01976759918034077</v>
       </c>
       <c r="O43" t="n">
-        <v>0.034116663039</v>
+        <v>0.02044269256293774</v>
       </c>
       <c r="P43" t="n">
-        <v>0.030608545989</v>
+        <v>0.01480239629745483</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.02690692991</v>
+        <v>0.03277145326137543</v>
       </c>
       <c r="R43" t="n">
-        <v>0.038968365639</v>
+        <v>0.03607865422964096</v>
       </c>
       <c r="S43" t="n">
-        <v>0.051909193397</v>
+        <v>0.03524420782923698</v>
       </c>
       <c r="T43" t="n">
-        <v>0.054342899472</v>
+        <v>0.01964199542999268</v>
       </c>
       <c r="U43" t="n">
-        <v>0.051873102784</v>
+        <v>0.03386112302541733</v>
       </c>
       <c r="V43" t="n">
-        <v>0.049726493657</v>
+        <v>0.01729151979088783</v>
       </c>
       <c r="W43" t="n">
-        <v>0.034684084356</v>
+        <v>0.0359368622303009</v>
       </c>
       <c r="X43" t="n">
-        <v>0.038844347</v>
+        <v>0.05043594166636467</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.037506055087</v>
+        <v>0.05344788730144501</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.035814192146</v>
+        <v>0.02690617926418781</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.035703513771</v>
+        <v>0.04562649875879288</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.044012621045</v>
+        <v>0.05257133394479752</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.050098419189</v>
+        <v>0.03695199266076088</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.023885451257</v>
+        <v>0.05034401640295982</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.037275176495</v>
+        <v>0.01694874465465546</v>
       </c>
       <c r="AF43" t="n">
-        <v>-0.002941269428</v>
+        <v>0.03027043864130974</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0.03113575279712677</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.01771489158272743</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.006915715523064137</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.01582815498113632</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.01985164172947407</v>
       </c>
     </row>
     <row r="44">
@@ -4874,94 +5529,109 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.029477983713</v>
+        <v>0.03111002221703529</v>
       </c>
       <c r="D44" t="n">
-        <v>0.027652172372</v>
+        <v>0.04807618632912636</v>
       </c>
       <c r="E44" t="n">
-        <v>0.017073411494</v>
+        <v>0.02880710177123547</v>
       </c>
       <c r="F44" t="n">
-        <v>0.022939449176</v>
+        <v>0.0356021523475647</v>
       </c>
       <c r="G44" t="n">
-        <v>0.017037738115</v>
+        <v>0.02831803262233734</v>
       </c>
       <c r="H44" t="n">
-        <v>0.055821213871</v>
+        <v>0.03328981623053551</v>
       </c>
       <c r="I44" t="n">
-        <v>0.020288642496</v>
+        <v>0.02899170853197575</v>
       </c>
       <c r="J44" t="n">
-        <v>0.002096673939</v>
+        <v>0.04349036514759064</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.002641023602</v>
+        <v>0.02348397113382816</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.007908054627</v>
+        <v>0.01691268384456635</v>
       </c>
       <c r="M44" t="n">
-        <v>0.04073478654</v>
+        <v>0.02317484840750694</v>
       </c>
       <c r="N44" t="n">
-        <v>0.025226183236</v>
+        <v>0.02421199530363083</v>
       </c>
       <c r="O44" t="n">
-        <v>0.03048600629</v>
+        <v>0.03043470531702042</v>
       </c>
       <c r="P44" t="n">
-        <v>0.038438972086</v>
+        <v>0.01930763013660908</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.021569807082</v>
+        <v>0.04064726829528809</v>
       </c>
       <c r="R44" t="n">
-        <v>0.040916457772</v>
+        <v>0.02978334575891495</v>
       </c>
       <c r="S44" t="n">
-        <v>0.032975982875</v>
+        <v>0.05140593275427818</v>
       </c>
       <c r="T44" t="n">
-        <v>0.024421934038</v>
+        <v>0.01903881132602692</v>
       </c>
       <c r="U44" t="n">
-        <v>0.029063947499</v>
+        <v>0.02899795211851597</v>
       </c>
       <c r="V44" t="n">
-        <v>0.025426011533</v>
+        <v>0.02332726866006851</v>
       </c>
       <c r="W44" t="n">
-        <v>0.00911382772</v>
+        <v>0.02873220853507519</v>
       </c>
       <c r="X44" t="n">
-        <v>0.02026454173</v>
+        <v>0.04790354520082474</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.012882495299</v>
+        <v>0.03358842805027962</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.011270774528</v>
+        <v>0.03334856405854225</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.015938779339</v>
+        <v>0.03308901935815811</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.021657494828</v>
+        <v>0.03892937302589417</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.026715405285</v>
+        <v>0.03180800750851631</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.017611628398</v>
+        <v>0.03690825402736664</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.015015841462</v>
+        <v>0.03323473408818245</v>
       </c>
       <c r="AF44" t="n">
-        <v>-0.009342016652000001</v>
+        <v>0.01676595956087112</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0.02541171759366989</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0.01443948969244957</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0.008985374122858047</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0.01013975776731968</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0.02688012272119522</v>
       </c>
     </row>
   </sheetData>
